--- a/research/traditional_assets/database/data/new_zealand/new_zealand_building_materials.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_building_materials.xlsx
@@ -1285,7 +1285,7 @@
         <v>3674.5</v>
       </c>
       <c r="N2">
-        <v>3407.18959716562</v>
+        <v>3407.18959716563</v>
       </c>
       <c r="O2">
         <v>2158.3</v>
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0856626422568786</v>
+        <v>0.08545518685855934</v>
       </c>
       <c r="C2">
-        <v>2981.085890155848</v>
+        <v>2957.05154478502</v>
       </c>
       <c r="D2">
-        <v>2791.685890155848</v>
+        <v>2806.29054478502</v>
       </c>
       <c r="E2">
-        <v>-2158.3</v>
+        <v>-2119.661</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>38.639</v>
       </c>
       <c r="G2">
         <v>189.4</v>
@@ -1579,28 +1579,28 @@
         <v>404.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.9435417</v>
       </c>
       <c r="N2">
-        <v>404.7</v>
+        <v>402.7564583</v>
       </c>
       <c r="O2">
-        <v>113.316</v>
+        <v>112.771808324</v>
       </c>
       <c r="P2">
-        <v>291.384</v>
+        <v>289.984649976</v>
       </c>
       <c r="Q2">
-        <v>396.684</v>
+        <v>395.284649976</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0856626422568786</v>
+        <v>0.08595255238238317</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9273106785769787</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>208.2281023350309</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08545518685855934</v>
+        <v>0.08524773146024008</v>
       </c>
       <c r="C3">
-        <v>2957.05154478502</v>
+        <v>2933.170811007623</v>
       </c>
       <c r="D3">
-        <v>2806.29054478502</v>
+        <v>2821.048811007623</v>
       </c>
       <c r="E3">
-        <v>-2119.661</v>
+        <v>-2081.022</v>
       </c>
       <c r="F3">
-        <v>38.639</v>
+        <v>77.27800000000001</v>
       </c>
       <c r="G3">
         <v>189.4</v>
@@ -1661,28 +1661,28 @@
         <v>404.7</v>
       </c>
       <c r="M3">
-        <v>1.9435417</v>
+        <v>3.8870834</v>
       </c>
       <c r="N3">
-        <v>402.7564583</v>
+        <v>400.8129166</v>
       </c>
       <c r="O3">
-        <v>112.771808324</v>
+        <v>112.227616648</v>
       </c>
       <c r="P3">
-        <v>289.984649976</v>
+        <v>288.585299952</v>
       </c>
       <c r="Q3">
-        <v>395.284649976</v>
+        <v>393.885299952</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08595255238238317</v>
+        <v>0.08624837904106131</v>
       </c>
       <c r="T3">
-        <v>0.9273106785769787</v>
+        <v>0.93414270302682</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>208.2281023350309</v>
+        <v>104.1140511675155</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08524773146024008</v>
+        <v>0.08504027606192081</v>
       </c>
       <c r="C4">
-        <v>2933.170811007623</v>
+        <v>2909.446125163878</v>
       </c>
       <c r="D4">
-        <v>2821.048811007623</v>
+        <v>2835.963125163878</v>
       </c>
       <c r="E4">
-        <v>-2081.022</v>
+        <v>-2042.383</v>
       </c>
       <c r="F4">
-        <v>77.27800000000001</v>
+        <v>115.917</v>
       </c>
       <c r="G4">
         <v>189.4</v>
@@ -1743,28 +1743,28 @@
         <v>404.7</v>
       </c>
       <c r="M4">
-        <v>3.8870834</v>
+        <v>5.8306251</v>
       </c>
       <c r="N4">
-        <v>400.8129166</v>
+        <v>398.8693749</v>
       </c>
       <c r="O4">
-        <v>112.227616648</v>
+        <v>111.683424972</v>
       </c>
       <c r="P4">
-        <v>288.585299952</v>
+        <v>287.185949928</v>
       </c>
       <c r="Q4">
-        <v>393.885299952</v>
+        <v>392.485949928</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08624837904106131</v>
+        <v>0.08655030521847507</v>
       </c>
       <c r="T4">
-        <v>0.93414270302682</v>
+        <v>0.9411155939601634</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.1140511675155</v>
+        <v>69.4093674450103</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08504027606192081</v>
+        <v>0.08483282066360155</v>
       </c>
       <c r="C5">
-        <v>2909.446125163878</v>
+        <v>2885.879975389591</v>
       </c>
       <c r="D5">
-        <v>2835.963125163878</v>
+        <v>2851.035975389591</v>
       </c>
       <c r="E5">
-        <v>-2042.383</v>
+        <v>-2003.744</v>
       </c>
       <c r="F5">
-        <v>115.917</v>
+        <v>154.556</v>
       </c>
       <c r="G5">
         <v>189.4</v>
@@ -1825,28 +1825,28 @@
         <v>404.7</v>
       </c>
       <c r="M5">
-        <v>5.8306251</v>
+        <v>7.774166800000001</v>
       </c>
       <c r="N5">
-        <v>398.8693749</v>
+        <v>396.9258332</v>
       </c>
       <c r="O5">
-        <v>111.683424972</v>
+        <v>111.139233296</v>
       </c>
       <c r="P5">
-        <v>287.185949928</v>
+        <v>285.786599904</v>
       </c>
       <c r="Q5">
-        <v>392.485949928</v>
+        <v>391.086599904</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08655030521847507</v>
+        <v>0.08685852152458495</v>
       </c>
       <c r="T5">
-        <v>0.9411155939601634</v>
+        <v>0.948233753454618</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.4093674450103</v>
+        <v>52.05702558375773</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08483282066360155</v>
+        <v>0.0846253652652823</v>
       </c>
       <c r="C6">
-        <v>2885.879975389591</v>
+        <v>2862.474902999948</v>
       </c>
       <c r="D6">
-        <v>2851.035975389591</v>
+        <v>2866.269902999948</v>
       </c>
       <c r="E6">
-        <v>-2003.744</v>
+        <v>-1965.105</v>
       </c>
       <c r="F6">
-        <v>154.556</v>
+        <v>193.195</v>
       </c>
       <c r="G6">
         <v>189.4</v>
@@ -1907,28 +1907,28 @@
         <v>404.7</v>
       </c>
       <c r="M6">
-        <v>7.774166800000001</v>
+        <v>9.717708500000001</v>
       </c>
       <c r="N6">
-        <v>396.9258332</v>
+        <v>394.9822915</v>
       </c>
       <c r="O6">
-        <v>111.139233296</v>
+        <v>110.59504162</v>
       </c>
       <c r="P6">
-        <v>285.786599904</v>
+        <v>284.38724988</v>
       </c>
       <c r="Q6">
-        <v>391.086599904</v>
+        <v>389.68724988</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08685852152458495</v>
+        <v>0.087173226595034</v>
       </c>
       <c r="T6">
-        <v>0.948233753454618</v>
+        <v>0.9555017689384295</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.05702558375773</v>
+        <v>41.64562046700618</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0846253652652823</v>
+        <v>0.08441790986696304</v>
       </c>
       <c r="C7">
-        <v>2862.474902999948</v>
+        <v>2839.233503917911</v>
       </c>
       <c r="D7">
-        <v>2866.269902999948</v>
+        <v>2881.667503917911</v>
       </c>
       <c r="E7">
-        <v>-1965.105</v>
+        <v>-1926.466</v>
       </c>
       <c r="F7">
-        <v>193.195</v>
+        <v>231.834</v>
       </c>
       <c r="G7">
         <v>189.4</v>
@@ -1989,28 +1989,28 @@
         <v>404.7</v>
       </c>
       <c r="M7">
-        <v>9.717708500000001</v>
+        <v>11.6612502</v>
       </c>
       <c r="N7">
-        <v>394.9822915</v>
+        <v>393.0387498</v>
       </c>
       <c r="O7">
-        <v>110.59504162</v>
+        <v>110.050849944</v>
       </c>
       <c r="P7">
-        <v>284.38724988</v>
+        <v>282.987899856</v>
       </c>
       <c r="Q7">
-        <v>389.68724988</v>
+        <v>388.287899856</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.087173226595034</v>
+        <v>0.08749462751804579</v>
       </c>
       <c r="T7">
-        <v>0.9555017689384295</v>
+        <v>0.9629244230495564</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.64562046700618</v>
+        <v>34.70468372250515</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08441790986696304</v>
+        <v>0.08421045446864379</v>
       </c>
       <c r="C8">
-        <v>2839.233503917911</v>
+        <v>2816.158430148905</v>
       </c>
       <c r="D8">
-        <v>2881.667503917911</v>
+        <v>2897.231430148905</v>
       </c>
       <c r="E8">
-        <v>-1926.466</v>
+        <v>-1887.827</v>
       </c>
       <c r="F8">
-        <v>231.834</v>
+        <v>270.473</v>
       </c>
       <c r="G8">
         <v>189.4</v>
@@ -2071,28 +2071,28 @@
         <v>404.7</v>
       </c>
       <c r="M8">
-        <v>11.6612502</v>
+        <v>13.6047919</v>
       </c>
       <c r="N8">
-        <v>393.0387498</v>
+        <v>391.0952081</v>
       </c>
       <c r="O8">
-        <v>110.050849944</v>
+        <v>109.506658268</v>
       </c>
       <c r="P8">
-        <v>282.987899856</v>
+        <v>281.588549832</v>
       </c>
       <c r="Q8">
-        <v>388.287899856</v>
+        <v>386.888549832</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08749462751804579</v>
+        <v>0.08782294028886428</v>
       </c>
       <c r="T8">
-        <v>0.9629244230495564</v>
+        <v>0.9705067041308149</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.70468372250516</v>
+        <v>29.74687176214728</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08421045446864378</v>
+        <v>0.08400299907032452</v>
       </c>
       <c r="C9">
-        <v>2816.158430148906</v>
+        <v>2793.252391303558</v>
       </c>
       <c r="D9">
-        <v>2897.231430148906</v>
+        <v>2912.964391303558</v>
       </c>
       <c r="E9">
-        <v>-1887.827</v>
+        <v>-1849.188</v>
       </c>
       <c r="F9">
-        <v>270.473</v>
+        <v>309.112</v>
       </c>
       <c r="G9">
         <v>189.4</v>
@@ -2153,28 +2153,28 @@
         <v>404.7</v>
       </c>
       <c r="M9">
-        <v>13.6047919</v>
+        <v>15.5483336</v>
       </c>
       <c r="N9">
-        <v>391.0952081</v>
+        <v>389.1516664</v>
       </c>
       <c r="O9">
-        <v>109.506658268</v>
+        <v>108.962466592</v>
       </c>
       <c r="P9">
-        <v>281.588549832</v>
+        <v>280.189199808</v>
       </c>
       <c r="Q9">
-        <v>386.888549832</v>
+        <v>385.489199808</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08782294028886428</v>
+        <v>0.08815839029383099</v>
       </c>
       <c r="T9">
-        <v>0.9705067041308149</v>
+        <v>0.9782538174094919</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.74687176214728</v>
+        <v>26.02851279187887</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08400299907032452</v>
+        <v>0.08379554367200526</v>
       </c>
       <c r="C10">
-        <v>2793.252391303558</v>
+        <v>2770.518156170311</v>
       </c>
       <c r="D10">
-        <v>2912.964391303558</v>
+        <v>2928.869156170311</v>
       </c>
       <c r="E10">
-        <v>-1849.188</v>
+        <v>-1810.549</v>
       </c>
       <c r="F10">
-        <v>309.112</v>
+        <v>347.751</v>
       </c>
       <c r="G10">
         <v>189.4</v>
@@ -2235,28 +2235,28 @@
         <v>404.7</v>
       </c>
       <c r="M10">
-        <v>15.5483336</v>
+        <v>17.4918753</v>
       </c>
       <c r="N10">
-        <v>389.1516664</v>
+        <v>387.2081247</v>
       </c>
       <c r="O10">
-        <v>108.962466592</v>
+        <v>108.418274916</v>
       </c>
       <c r="P10">
-        <v>280.189199808</v>
+        <v>278.789849784</v>
       </c>
       <c r="Q10">
-        <v>385.489199808</v>
+        <v>384.089849784</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08815839029383099</v>
+        <v>0.08850121282637941</v>
       </c>
       <c r="T10">
-        <v>0.9782538174094919</v>
+        <v>0.9861711969140742</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.02851279187887</v>
+        <v>23.13645581500344</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08379554367200526</v>
+        <v>0.08358808827368601</v>
       </c>
       <c r="C11">
-        <v>2770.518156170311</v>
+        <v>2747.95855433985</v>
       </c>
       <c r="D11">
-        <v>2928.869156170311</v>
+        <v>2944.94855433985</v>
       </c>
       <c r="E11">
-        <v>-1810.549</v>
+        <v>-1771.91</v>
       </c>
       <c r="F11">
-        <v>347.751</v>
+        <v>386.39</v>
       </c>
       <c r="G11">
         <v>189.4</v>
@@ -2317,28 +2317,28 @@
         <v>404.7</v>
       </c>
       <c r="M11">
-        <v>17.4918753</v>
+        <v>19.435417</v>
       </c>
       <c r="N11">
-        <v>387.2081247</v>
+        <v>385.264583</v>
       </c>
       <c r="O11">
-        <v>108.418274916</v>
+        <v>107.87408324</v>
       </c>
       <c r="P11">
-        <v>278.789849784</v>
+        <v>277.39049976</v>
       </c>
       <c r="Q11">
-        <v>384.089849784</v>
+        <v>382.69049976</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08850121282637941</v>
+        <v>0.08885165363742889</v>
       </c>
       <c r="T11">
-        <v>0.9861711969140742</v>
+        <v>0.9942645181854248</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.13645581500344</v>
+        <v>20.8228102335031</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08358808827368601</v>
+        <v>0.08338063287536673</v>
       </c>
       <c r="C12">
-        <v>2747.95855433985</v>
+        <v>2725.576477883328</v>
       </c>
       <c r="D12">
-        <v>2944.94855433985</v>
+        <v>2961.205477883328</v>
       </c>
       <c r="E12">
-        <v>-1771.91</v>
+        <v>-1733.271</v>
       </c>
       <c r="F12">
-        <v>386.39</v>
+        <v>425.029</v>
       </c>
       <c r="G12">
         <v>189.4</v>
@@ -2399,28 +2399,28 @@
         <v>404.7</v>
       </c>
       <c r="M12">
-        <v>19.435417</v>
+        <v>21.3789587</v>
       </c>
       <c r="N12">
-        <v>385.264583</v>
+        <v>383.3210413</v>
       </c>
       <c r="O12">
-        <v>107.87408324</v>
+        <v>107.329891564</v>
       </c>
       <c r="P12">
-        <v>277.39049976</v>
+        <v>275.991149736</v>
       </c>
       <c r="Q12">
-        <v>382.69049976</v>
+        <v>381.291149736</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08885165363742889</v>
+        <v>0.08920996952288397</v>
       </c>
       <c r="T12">
-        <v>0.9942645181854248</v>
+        <v>1.002539711844896</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.82281023350309</v>
+        <v>18.92982748500281</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08338063287536673</v>
+        <v>0.08317317747704749</v>
       </c>
       <c r="C13">
-        <v>2725.576477883328</v>
+        <v>2703.374883086477</v>
       </c>
       <c r="D13">
-        <v>2961.205477883328</v>
+        <v>2977.642883086477</v>
       </c>
       <c r="E13">
-        <v>-1733.271</v>
+        <v>-1694.632</v>
       </c>
       <c r="F13">
-        <v>425.029</v>
+        <v>463.668</v>
       </c>
       <c r="G13">
         <v>189.4</v>
@@ -2481,28 +2481,28 @@
         <v>404.7</v>
       </c>
       <c r="M13">
-        <v>21.3789587</v>
+        <v>23.3225004</v>
       </c>
       <c r="N13">
-        <v>383.3210413</v>
+        <v>381.3774996</v>
       </c>
       <c r="O13">
-        <v>107.329891564</v>
+        <v>106.785699888</v>
       </c>
       <c r="P13">
-        <v>275.991149736</v>
+        <v>274.591799712</v>
       </c>
       <c r="Q13">
-        <v>381.291149736</v>
+        <v>379.891799712</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08920996952288397</v>
+        <v>0.08957642895119032</v>
       </c>
       <c r="T13">
-        <v>1.002539711844896</v>
+        <v>1.011002978087536</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.92982748500281</v>
+        <v>17.35234186125258</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08317317747704749</v>
+        <v>0.08296572207872822</v>
       </c>
       <c r="C14">
-        <v>2703.374883086477</v>
+        <v>2681.356792241819</v>
       </c>
       <c r="D14">
-        <v>2977.642883086477</v>
+        <v>2994.263792241818</v>
       </c>
       <c r="E14">
-        <v>-1694.632</v>
+        <v>-1655.993</v>
       </c>
       <c r="F14">
-        <v>463.668</v>
+        <v>502.307</v>
       </c>
       <c r="G14">
         <v>189.4</v>
@@ -2563,28 +2563,28 @@
         <v>404.7</v>
       </c>
       <c r="M14">
-        <v>23.3225004</v>
+        <v>25.2660421</v>
       </c>
       <c r="N14">
-        <v>381.3774996</v>
+        <v>379.4339579</v>
       </c>
       <c r="O14">
-        <v>106.785699888</v>
+        <v>106.241508212</v>
       </c>
       <c r="P14">
-        <v>274.591799712</v>
+        <v>273.192449688</v>
       </c>
       <c r="Q14">
-        <v>379.891799712</v>
+        <v>378.492449688</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08957642895119032</v>
+        <v>0.08995131273417037</v>
       </c>
       <c r="T14">
-        <v>1.011002978087536</v>
+        <v>1.019660802174835</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.35234186125258</v>
+        <v>16.01754633346392</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08296572207872822</v>
+        <v>0.08275826668040895</v>
       </c>
       <c r="C15">
-        <v>2681.356792241819</v>
+        <v>2659.525295501212</v>
       </c>
       <c r="D15">
-        <v>2994.263792241818</v>
+        <v>3011.071295501212</v>
       </c>
       <c r="E15">
-        <v>-1655.993</v>
+        <v>-1617.354</v>
       </c>
       <c r="F15">
-        <v>502.307</v>
+        <v>540.946</v>
       </c>
       <c r="G15">
         <v>189.4</v>
@@ -2645,28 +2645,28 @@
         <v>404.7</v>
       </c>
       <c r="M15">
-        <v>25.2660421</v>
+        <v>27.2095838</v>
       </c>
       <c r="N15">
-        <v>379.4339579</v>
+        <v>377.4904162</v>
       </c>
       <c r="O15">
-        <v>106.241508212</v>
+        <v>105.697316536</v>
       </c>
       <c r="P15">
-        <v>273.192449688</v>
+        <v>271.793099664</v>
       </c>
       <c r="Q15">
-        <v>378.492449688</v>
+        <v>377.093099664</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08995131273417037</v>
+        <v>0.09033491474466157</v>
       </c>
       <c r="T15">
-        <v>1.019660802174835</v>
+        <v>1.028519971008351</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.01754633346392</v>
+        <v>14.87343588107364</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08275826668040895</v>
+        <v>0.0825508112820897</v>
       </c>
       <c r="C16">
-        <v>2659.525295501212</v>
+        <v>2637.883552791156</v>
       </c>
       <c r="D16">
-        <v>3011.071295501212</v>
+        <v>3028.068552791156</v>
       </c>
       <c r="E16">
-        <v>-1617.354</v>
+        <v>-1578.715</v>
       </c>
       <c r="F16">
-        <v>540.946</v>
+        <v>579.5850000000002</v>
       </c>
       <c r="G16">
         <v>189.4</v>
@@ -2727,28 +2727,28 @@
         <v>404.7</v>
       </c>
       <c r="M16">
-        <v>27.2095838</v>
+        <v>29.15312550000001</v>
       </c>
       <c r="N16">
-        <v>377.4904162</v>
+        <v>375.5468745</v>
       </c>
       <c r="O16">
-        <v>105.697316536</v>
+        <v>105.15312486</v>
       </c>
       <c r="P16">
-        <v>271.793099664</v>
+        <v>270.39374964</v>
       </c>
       <c r="Q16">
-        <v>377.093099664</v>
+        <v>375.69374964</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09033491474466157</v>
+        <v>0.09072754268481141</v>
       </c>
       <c r="T16">
-        <v>1.028519971008351</v>
+        <v>1.037587590873243</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.87343588107364</v>
+        <v>13.88187348900206</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0825508112820897</v>
+        <v>0.08234335588377044</v>
       </c>
       <c r="C17">
-        <v>2637.883552791156</v>
+        <v>2616.434795793341</v>
       </c>
       <c r="D17">
-        <v>3028.068552791156</v>
+        <v>3045.258795793341</v>
       </c>
       <c r="E17">
-        <v>-1578.715</v>
+        <v>-1540.076</v>
       </c>
       <c r="F17">
-        <v>579.585</v>
+        <v>618.224</v>
       </c>
       <c r="G17">
         <v>189.4</v>
@@ -2809,28 +2809,28 @@
         <v>404.7</v>
       </c>
       <c r="M17">
-        <v>29.1531255</v>
+        <v>31.0966672</v>
       </c>
       <c r="N17">
-        <v>375.5468745</v>
+        <v>373.6033328</v>
       </c>
       <c r="O17">
-        <v>105.15312486</v>
+        <v>104.608933184</v>
       </c>
       <c r="P17">
-        <v>270.39374964</v>
+        <v>268.994399616</v>
       </c>
       <c r="Q17">
-        <v>375.69374964</v>
+        <v>374.294399616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09072754268481141</v>
+        <v>0.09112951890925053</v>
       </c>
       <c r="T17">
-        <v>1.037587590873243</v>
+        <v>1.046871106449204</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.88187348900206</v>
+        <v>13.01425639593943</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08234335588377044</v>
+        <v>0.08231950048545117</v>
       </c>
       <c r="C18">
-        <v>2616.434795793341</v>
+        <v>2579.785030601956</v>
       </c>
       <c r="D18">
-        <v>3045.258795793341</v>
+        <v>3047.248030601956</v>
       </c>
       <c r="E18">
-        <v>-1540.076</v>
+        <v>-1501.437</v>
       </c>
       <c r="F18">
-        <v>618.224</v>
+        <v>656.8630000000001</v>
       </c>
       <c r="G18">
         <v>189.4</v>
@@ -2891,45 +2891,45 @@
         <v>404.7</v>
       </c>
       <c r="M18">
-        <v>31.0966672</v>
+        <v>34.02550340000001</v>
       </c>
       <c r="N18">
-        <v>373.6033328</v>
+        <v>370.6744966</v>
       </c>
       <c r="O18">
-        <v>104.608933184</v>
+        <v>103.788859048</v>
       </c>
       <c r="P18">
-        <v>268.994399616</v>
+        <v>266.885637552</v>
       </c>
       <c r="Q18">
-        <v>374.294399616</v>
+        <v>372.185637552</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09112951890925053</v>
+        <v>0.0915411813077725</v>
       </c>
       <c r="T18">
-        <v>1.046871106449204</v>
+        <v>1.05637832119567</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.28</v>
       </c>
       <c r="W18">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.01425639593943</v>
+        <v>11.89401947246429</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08231950048545117</v>
+        <v>0.08212284508713193</v>
       </c>
       <c r="C19">
-        <v>2579.785030601956</v>
+        <v>2557.644126326507</v>
       </c>
       <c r="D19">
-        <v>3047.248030601956</v>
+        <v>3063.746126326507</v>
       </c>
       <c r="E19">
-        <v>-1501.437</v>
+        <v>-1462.798</v>
       </c>
       <c r="F19">
-        <v>656.8630000000001</v>
+        <v>695.5020000000001</v>
       </c>
       <c r="G19">
         <v>189.4</v>
@@ -2973,28 +2973,28 @@
         <v>404.7</v>
       </c>
       <c r="M19">
-        <v>34.02550340000001</v>
+        <v>36.0270036</v>
       </c>
       <c r="N19">
-        <v>370.6744966</v>
+        <v>368.6729964</v>
       </c>
       <c r="O19">
-        <v>103.788859048</v>
+        <v>103.228438992</v>
       </c>
       <c r="P19">
-        <v>266.885637552</v>
+        <v>265.444557408</v>
       </c>
       <c r="Q19">
-        <v>372.185637552</v>
+        <v>370.744557408</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0915411813077725</v>
+        <v>0.09196288425259991</v>
       </c>
       <c r="T19">
-        <v>1.05637832119567</v>
+        <v>1.066117419228635</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.89401947246429</v>
+        <v>11.23324061288294</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08212284508713193</v>
+        <v>0.08192618968881266</v>
       </c>
       <c r="C20">
-        <v>2557.644126326507</v>
+        <v>2535.682839088682</v>
       </c>
       <c r="D20">
-        <v>3063.746126326507</v>
+        <v>3080.423839088682</v>
       </c>
       <c r="E20">
-        <v>-1462.798</v>
+        <v>-1424.159</v>
       </c>
       <c r="F20">
-        <v>695.502</v>
+        <v>734.1410000000001</v>
       </c>
       <c r="G20">
         <v>189.4</v>
@@ -3055,28 +3055,28 @@
         <v>404.7</v>
       </c>
       <c r="M20">
-        <v>36.02700359999999</v>
+        <v>38.0285038</v>
       </c>
       <c r="N20">
-        <v>368.6729964</v>
+        <v>366.6714962</v>
       </c>
       <c r="O20">
-        <v>103.228438992</v>
+        <v>102.668018936</v>
       </c>
       <c r="P20">
-        <v>265.444557408</v>
+        <v>264.003477264</v>
       </c>
       <c r="Q20">
-        <v>370.744557408</v>
+        <v>369.303477264</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09196288425259991</v>
+        <v>0.0923949996158181</v>
       </c>
       <c r="T20">
-        <v>1.066117419228635</v>
+        <v>1.07609698881797</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.23324061288294</v>
+        <v>10.64201742273121</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08192618968881266</v>
+        <v>0.08172953429049339</v>
       </c>
       <c r="C21">
-        <v>2535.682839088682</v>
+        <v>2513.904118216443</v>
       </c>
       <c r="D21">
-        <v>3080.423839088682</v>
+        <v>3097.284118216443</v>
       </c>
       <c r="E21">
-        <v>-1424.159</v>
+        <v>-1385.52</v>
       </c>
       <c r="F21">
-        <v>734.1410000000001</v>
+        <v>772.7800000000001</v>
       </c>
       <c r="G21">
         <v>189.4</v>
@@ -3137,28 +3137,28 @@
         <v>404.7</v>
       </c>
       <c r="M21">
-        <v>38.0285038</v>
+        <v>40.03000400000001</v>
       </c>
       <c r="N21">
-        <v>366.6714962</v>
+        <v>364.669996</v>
       </c>
       <c r="O21">
-        <v>102.668018936</v>
+        <v>102.10759888</v>
       </c>
       <c r="P21">
-        <v>264.003477264</v>
+        <v>262.56239712</v>
       </c>
       <c r="Q21">
-        <v>369.303477264</v>
+        <v>367.86239712</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0923949996158181</v>
+        <v>0.09283791786311674</v>
       </c>
       <c r="T21">
-        <v>1.07609698881797</v>
+        <v>1.086326047647038</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.64201742273121</v>
+        <v>10.10991655159465</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08172953429049339</v>
+        <v>0.08178991889217414</v>
       </c>
       <c r="C22">
-        <v>2513.904118216443</v>
+        <v>2470.068433324461</v>
       </c>
       <c r="D22">
-        <v>3097.284118216443</v>
+        <v>3092.087433324461</v>
       </c>
       <c r="E22">
-        <v>-1385.52</v>
+        <v>-1346.881</v>
       </c>
       <c r="F22">
-        <v>772.7800000000001</v>
+        <v>811.4190000000001</v>
       </c>
       <c r="G22">
         <v>189.4</v>
@@ -3219,45 +3219,45 @@
         <v>404.7</v>
       </c>
       <c r="M22">
-        <v>40.03000400000001</v>
+        <v>43.41091650000001</v>
       </c>
       <c r="N22">
-        <v>364.669996</v>
+        <v>361.2890835</v>
       </c>
       <c r="O22">
-        <v>102.10759888</v>
+        <v>101.16094338</v>
       </c>
       <c r="P22">
-        <v>262.56239712</v>
+        <v>260.12814012</v>
       </c>
       <c r="Q22">
-        <v>367.86239712</v>
+        <v>365.42814012</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09283791786311674</v>
+        <v>0.09329204923060018</v>
       </c>
       <c r="T22">
-        <v>1.086326047647038</v>
+        <v>1.096814069990766</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.28</v>
       </c>
       <c r="W22">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.10991655159465</v>
+        <v>9.322539873121544</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08178991889217414</v>
+        <v>0.08160550349385487</v>
       </c>
       <c r="C23">
-        <v>2470.068433324461</v>
+        <v>2447.355156467899</v>
       </c>
       <c r="D23">
-        <v>3092.087433324461</v>
+        <v>3108.013156467899</v>
       </c>
       <c r="E23">
-        <v>-1346.881</v>
+        <v>-1308.242</v>
       </c>
       <c r="F23">
-        <v>811.419</v>
+        <v>850.058</v>
       </c>
       <c r="G23">
         <v>189.4</v>
@@ -3301,28 +3301,28 @@
         <v>404.7</v>
       </c>
       <c r="M23">
-        <v>43.4109165</v>
+        <v>45.478103</v>
       </c>
       <c r="N23">
-        <v>361.2890835</v>
+        <v>359.221897</v>
       </c>
       <c r="O23">
-        <v>101.16094338</v>
+        <v>100.58213116</v>
       </c>
       <c r="P23">
-        <v>260.12814012</v>
+        <v>258.63976584</v>
       </c>
       <c r="Q23">
-        <v>365.42814012</v>
+        <v>363.93976584</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09329204923060018</v>
+        <v>0.09375782499212164</v>
       </c>
       <c r="T23">
-        <v>1.096814069990766</v>
+        <v>1.107571015984333</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.322539873121546</v>
+        <v>8.898788060706931</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08160550349385487</v>
+        <v>0.08142108809553561</v>
       </c>
       <c r="C24">
-        <v>2447.355156467899</v>
+        <v>2424.806779042209</v>
       </c>
       <c r="D24">
-        <v>3108.013156467899</v>
+        <v>3124.103779042209</v>
       </c>
       <c r="E24">
-        <v>-1308.242</v>
+        <v>-1269.603</v>
       </c>
       <c r="F24">
-        <v>850.058</v>
+        <v>888.697</v>
       </c>
       <c r="G24">
         <v>189.4</v>
@@ -3383,28 +3383,28 @@
         <v>404.7</v>
       </c>
       <c r="M24">
-        <v>45.478103</v>
+        <v>47.5452895</v>
       </c>
       <c r="N24">
-        <v>359.221897</v>
+        <v>357.1547105</v>
       </c>
       <c r="O24">
-        <v>100.58213116</v>
+        <v>100.00331894</v>
       </c>
       <c r="P24">
-        <v>258.63976584</v>
+        <v>257.15139156</v>
       </c>
       <c r="Q24">
-        <v>363.93976584</v>
+        <v>362.45139156</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09375782499212164</v>
+        <v>0.09423569882537093</v>
       </c>
       <c r="T24">
-        <v>1.107571015984333</v>
+        <v>1.118607363172539</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.898788060706931</v>
+        <v>8.51188423198054</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08142108809553561</v>
+        <v>0.08123667269721635</v>
       </c>
       <c r="C25">
-        <v>2424.806779042209</v>
+        <v>2402.42587549854</v>
       </c>
       <c r="D25">
-        <v>3124.103779042209</v>
+        <v>3140.36187549854</v>
       </c>
       <c r="E25">
-        <v>-1269.603</v>
+        <v>-1230.964</v>
       </c>
       <c r="F25">
-        <v>888.697</v>
+        <v>927.3360000000001</v>
       </c>
       <c r="G25">
         <v>189.4</v>
@@ -3465,28 +3465,28 @@
         <v>404.7</v>
       </c>
       <c r="M25">
-        <v>47.5452895</v>
+        <v>49.61247600000001</v>
       </c>
       <c r="N25">
-        <v>357.1547105</v>
+        <v>355.087524</v>
       </c>
       <c r="O25">
-        <v>100.00331894</v>
+        <v>99.42450672</v>
       </c>
       <c r="P25">
-        <v>257.15139156</v>
+        <v>255.66301728</v>
       </c>
       <c r="Q25">
-        <v>362.45139156</v>
+        <v>360.96301728</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09423569882537093</v>
+        <v>0.094726148285811</v>
       </c>
       <c r="T25">
-        <v>1.118607363172539</v>
+        <v>1.129934140549908</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.51188423198054</v>
+        <v>8.157222388981349</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08123667269721635</v>
+        <v>0.0810522572988971</v>
       </c>
       <c r="C26">
-        <v>2402.42587549854</v>
+        <v>2380.21507415902</v>
       </c>
       <c r="D26">
-        <v>3140.36187549854</v>
+        <v>3156.79007415902</v>
       </c>
       <c r="E26">
-        <v>-1230.964</v>
+        <v>-1192.325</v>
       </c>
       <c r="F26">
-        <v>927.336</v>
+        <v>965.975</v>
       </c>
       <c r="G26">
         <v>189.4</v>
@@ -3547,28 +3547,28 @@
         <v>404.7</v>
       </c>
       <c r="M26">
-        <v>49.612476</v>
+        <v>51.6796625</v>
       </c>
       <c r="N26">
-        <v>355.087524</v>
+        <v>353.0203375</v>
       </c>
       <c r="O26">
-        <v>99.42450672</v>
+        <v>98.84569450000001</v>
       </c>
       <c r="P26">
-        <v>255.66301728</v>
+        <v>254.174643</v>
       </c>
       <c r="Q26">
-        <v>360.96301728</v>
+        <v>359.474643</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.094726148285811</v>
+        <v>0.09522967639852947</v>
       </c>
       <c r="T26">
-        <v>1.129934140549908</v>
+        <v>1.141562965324006</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.157222388981351</v>
+        <v>7.830933493422098</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0810522572988971</v>
+        <v>0.08101760190057784</v>
       </c>
       <c r="C27">
-        <v>2380.21507415902</v>
+        <v>2344.682470152112</v>
       </c>
       <c r="D27">
-        <v>3156.79007415902</v>
+        <v>3159.896470152112</v>
       </c>
       <c r="E27">
-        <v>-1192.325</v>
+        <v>-1153.686</v>
       </c>
       <c r="F27">
-        <v>965.975</v>
+        <v>1004.614</v>
       </c>
       <c r="G27">
         <v>189.4</v>
@@ -3629,45 +3629,45 @@
         <v>404.7</v>
       </c>
       <c r="M27">
-        <v>51.6796625</v>
+        <v>54.5505402</v>
       </c>
       <c r="N27">
-        <v>353.0203375</v>
+        <v>350.1494598</v>
       </c>
       <c r="O27">
-        <v>98.84569450000001</v>
+        <v>98.04184874400001</v>
       </c>
       <c r="P27">
-        <v>254.174643</v>
+        <v>252.107611056</v>
       </c>
       <c r="Q27">
-        <v>359.474643</v>
+        <v>357.407611056</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09522967639852947</v>
+        <v>0.09574681337915925</v>
       </c>
       <c r="T27">
-        <v>1.141562965324006</v>
+        <v>1.153506082659567</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.28</v>
       </c>
       <c r="W27">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.830933493422098</v>
+        <v>7.418808292571225</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08101760190057784</v>
+        <v>0.08083894650225858</v>
       </c>
       <c r="C28">
-        <v>2344.682470152112</v>
+        <v>2322.155043668921</v>
       </c>
       <c r="D28">
-        <v>3159.896470152112</v>
+        <v>3176.008043668921</v>
       </c>
       <c r="E28">
-        <v>-1153.686</v>
+        <v>-1115.047</v>
       </c>
       <c r="F28">
-        <v>1004.614</v>
+        <v>1043.253</v>
       </c>
       <c r="G28">
         <v>189.4</v>
@@ -3711,28 +3711,28 @@
         <v>404.7</v>
       </c>
       <c r="M28">
-        <v>54.5505402</v>
+        <v>56.64863790000001</v>
       </c>
       <c r="N28">
-        <v>350.1494598</v>
+        <v>348.0513621</v>
       </c>
       <c r="O28">
-        <v>98.04184874400001</v>
+        <v>97.45438138800002</v>
       </c>
       <c r="P28">
-        <v>252.107611056</v>
+        <v>250.596980712</v>
       </c>
       <c r="Q28">
-        <v>357.407611056</v>
+        <v>355.896980712</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09574681337915925</v>
+        <v>0.09627811849624462</v>
       </c>
       <c r="T28">
-        <v>1.153506082659567</v>
+        <v>1.165776408689252</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.418808292571225</v>
+        <v>7.144037615068586</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08083894650225858</v>
+        <v>0.08066029110393932</v>
       </c>
       <c r="C29">
-        <v>2322.155043668921</v>
+        <v>2299.792757492539</v>
       </c>
       <c r="D29">
-        <v>3176.008043668921</v>
+        <v>3192.284757492539</v>
       </c>
       <c r="E29">
-        <v>-1115.047</v>
+        <v>-1076.408</v>
       </c>
       <c r="F29">
-        <v>1043.253</v>
+        <v>1081.892</v>
       </c>
       <c r="G29">
         <v>189.4</v>
@@ -3793,28 +3793,28 @@
         <v>404.7</v>
       </c>
       <c r="M29">
-        <v>56.64863790000001</v>
+        <v>58.7467356</v>
       </c>
       <c r="N29">
-        <v>348.0513621</v>
+        <v>345.9532644</v>
       </c>
       <c r="O29">
-        <v>97.45438138800002</v>
+        <v>96.866914032</v>
       </c>
       <c r="P29">
-        <v>250.596980712</v>
+        <v>249.086350368</v>
       </c>
       <c r="Q29">
-        <v>355.896980712</v>
+        <v>354.386350368</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09627811849624462</v>
+        <v>0.09682418208880461</v>
       </c>
       <c r="T29">
-        <v>1.165776408689252</v>
+        <v>1.178387577108652</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.144037615068586</v>
+        <v>6.888893414530423</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08066029110393932</v>
+        <v>0.08048163570562004</v>
       </c>
       <c r="C30">
-        <v>2299.792757492539</v>
+        <v>2277.59816368316</v>
       </c>
       <c r="D30">
-        <v>3192.284757492539</v>
+        <v>3208.729163683161</v>
       </c>
       <c r="E30">
-        <v>-1076.408</v>
+        <v>-1037.769</v>
       </c>
       <c r="F30">
-        <v>1081.892</v>
+        <v>1120.531</v>
       </c>
       <c r="G30">
         <v>189.4</v>
@@ -3875,28 +3875,28 @@
         <v>404.7</v>
       </c>
       <c r="M30">
-        <v>58.7467356</v>
+        <v>60.84483330000001</v>
       </c>
       <c r="N30">
-        <v>345.9532644</v>
+        <v>343.8551667</v>
       </c>
       <c r="O30">
-        <v>96.866914032</v>
+        <v>96.27944667600001</v>
       </c>
       <c r="P30">
-        <v>249.086350368</v>
+        <v>247.575720024</v>
       </c>
       <c r="Q30">
-        <v>354.386350368</v>
+        <v>352.875720024</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09682418208880461</v>
+        <v>0.09738562775439444</v>
       </c>
       <c r="T30">
-        <v>1.178387577108652</v>
+        <v>1.191353989708879</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.888893414530423</v>
+        <v>6.651345365753511</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08048163570562004</v>
+        <v>0.08030298030730081</v>
       </c>
       <c r="C31">
-        <v>2277.598163683161</v>
+        <v>2255.573867158937</v>
       </c>
       <c r="D31">
-        <v>3208.729163683161</v>
+        <v>3225.343867158937</v>
       </c>
       <c r="E31">
-        <v>-1037.769</v>
+        <v>-999.1300000000001</v>
       </c>
       <c r="F31">
-        <v>1120.531</v>
+        <v>1159.17</v>
       </c>
       <c r="G31">
         <v>189.4</v>
@@ -3957,28 +3957,28 @@
         <v>404.7</v>
       </c>
       <c r="M31">
-        <v>60.8448333</v>
+        <v>62.94293100000001</v>
       </c>
       <c r="N31">
-        <v>343.8551667</v>
+        <v>341.757069</v>
       </c>
       <c r="O31">
-        <v>96.27944667600001</v>
+        <v>95.69197932000002</v>
       </c>
       <c r="P31">
-        <v>247.575720024</v>
+        <v>246.06508968</v>
       </c>
       <c r="Q31">
-        <v>352.875720024</v>
+        <v>351.36508968</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09738562775439444</v>
+        <v>0.09796311472471544</v>
       </c>
       <c r="T31">
-        <v>1.191353989708879</v>
+        <v>1.204690871240541</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.651345365753513</v>
+        <v>6.429633853561728</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08030298030730081</v>
+        <v>0.08012432490898153</v>
       </c>
       <c r="C32">
-        <v>2255.573867158937</v>
+        <v>2233.722527071606</v>
       </c>
       <c r="D32">
-        <v>3225.343867158937</v>
+        <v>3242.131527071606</v>
       </c>
       <c r="E32">
-        <v>-999.1300000000001</v>
+        <v>-960.4910000000002</v>
       </c>
       <c r="F32">
-        <v>1159.17</v>
+        <v>1197.809</v>
       </c>
       <c r="G32">
         <v>189.4</v>
@@ -4039,28 +4039,28 @@
         <v>404.7</v>
       </c>
       <c r="M32">
-        <v>62.94293100000001</v>
+        <v>65.0410287</v>
       </c>
       <c r="N32">
-        <v>341.757069</v>
+        <v>339.6589713</v>
       </c>
       <c r="O32">
-        <v>95.69197932000002</v>
+        <v>95.104511964</v>
       </c>
       <c r="P32">
-        <v>246.06508968</v>
+        <v>244.554459336</v>
       </c>
       <c r="Q32">
-        <v>351.36508968</v>
+        <v>349.854459336</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09796311472471544</v>
+        <v>0.09855734044779933</v>
       </c>
       <c r="T32">
-        <v>1.204690871240541</v>
+        <v>1.218414329048483</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.429633853561728</v>
+        <v>6.222226309898446</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08012432490898153</v>
+        <v>0.08017606951066227</v>
       </c>
       <c r="C33">
-        <v>2233.722527071606</v>
+        <v>2190.203306416571</v>
       </c>
       <c r="D33">
-        <v>3242.131527071606</v>
+        <v>3237.251306416571</v>
       </c>
       <c r="E33">
-        <v>-960.4910000000002</v>
+        <v>-921.8520000000001</v>
       </c>
       <c r="F33">
-        <v>1197.809</v>
+        <v>1236.448</v>
       </c>
       <c r="G33">
         <v>189.4</v>
@@ -4121,45 +4121,45 @@
         <v>404.7</v>
       </c>
       <c r="M33">
-        <v>65.0410287</v>
+        <v>68.3755744</v>
       </c>
       <c r="N33">
-        <v>339.6589713</v>
+        <v>336.3244256</v>
       </c>
       <c r="O33">
-        <v>95.104511964</v>
+        <v>94.170839168</v>
       </c>
       <c r="P33">
-        <v>244.554459336</v>
+        <v>242.153586432</v>
       </c>
       <c r="Q33">
-        <v>349.854459336</v>
+        <v>347.453586432</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09855734044779933</v>
+        <v>0.09916904339803276</v>
       </c>
       <c r="T33">
-        <v>1.218414329048483</v>
+        <v>1.232541417968424</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.28</v>
       </c>
       <c r="W33">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.222226309898446</v>
+        <v>5.918780259636107</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08017606951066227</v>
+        <v>0.08000461411234301</v>
       </c>
       <c r="C34">
-        <v>2190.203306416571</v>
+        <v>2167.791480048121</v>
       </c>
       <c r="D34">
-        <v>3237.251306416571</v>
+        <v>3253.478480048121</v>
       </c>
       <c r="E34">
-        <v>-921.8520000000001</v>
+        <v>-883.2130000000002</v>
       </c>
       <c r="F34">
-        <v>1236.448</v>
+        <v>1275.087</v>
       </c>
       <c r="G34">
         <v>189.4</v>
@@ -4203,28 +4203,28 @@
         <v>404.7</v>
       </c>
       <c r="M34">
-        <v>68.3755744</v>
+        <v>70.51231110000001</v>
       </c>
       <c r="N34">
-        <v>336.3244256</v>
+        <v>334.1876889</v>
       </c>
       <c r="O34">
-        <v>94.170839168</v>
+        <v>93.57255289200002</v>
       </c>
       <c r="P34">
-        <v>242.153586432</v>
+        <v>240.615136008</v>
       </c>
       <c r="Q34">
-        <v>347.453586432</v>
+        <v>345.915136008</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09916904339803276</v>
+        <v>0.0997990061378254</v>
       </c>
       <c r="T34">
-        <v>1.232541417968424</v>
+        <v>1.247090211035229</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.918780259636107</v>
+        <v>5.739423282071377</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08000461411234301</v>
+        <v>0.07983315871402376</v>
       </c>
       <c r="C35">
-        <v>2167.791480048121</v>
+        <v>2145.543155195471</v>
       </c>
       <c r="D35">
-        <v>3253.478480048121</v>
+        <v>3269.869155195471</v>
       </c>
       <c r="E35">
-        <v>-883.2130000000002</v>
+        <v>-844.5740000000001</v>
       </c>
       <c r="F35">
-        <v>1275.087</v>
+        <v>1313.726</v>
       </c>
       <c r="G35">
         <v>189.4</v>
@@ -4285,28 +4285,28 @@
         <v>404.7</v>
       </c>
       <c r="M35">
-        <v>70.51231110000001</v>
+        <v>72.64904780000001</v>
       </c>
       <c r="N35">
-        <v>334.1876889</v>
+        <v>332.0509522</v>
       </c>
       <c r="O35">
-        <v>93.57255289200002</v>
+        <v>92.97426661600001</v>
       </c>
       <c r="P35">
-        <v>240.615136008</v>
+        <v>239.076685584</v>
       </c>
       <c r="Q35">
-        <v>345.915136008</v>
+        <v>344.376685584</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0997990061378254</v>
+        <v>0.1004480586576118</v>
       </c>
       <c r="T35">
-        <v>1.247090211035229</v>
+        <v>1.262079876619209</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.739423282071377</v>
+        <v>5.570616714951631</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07983315871402376</v>
+        <v>0.07966170331570449</v>
       </c>
       <c r="C36">
-        <v>2145.543155195471</v>
+        <v>2123.460815480068</v>
       </c>
       <c r="D36">
-        <v>3269.869155195471</v>
+        <v>3286.425815480068</v>
       </c>
       <c r="E36">
-        <v>-844.5740000000001</v>
+        <v>-805.9349999999999</v>
       </c>
       <c r="F36">
-        <v>1313.726</v>
+        <v>1352.365</v>
       </c>
       <c r="G36">
         <v>189.4</v>
@@ -4367,28 +4367,28 @@
         <v>404.7</v>
       </c>
       <c r="M36">
-        <v>72.64904780000001</v>
+        <v>74.78578450000002</v>
       </c>
       <c r="N36">
-        <v>332.0509522</v>
+        <v>329.9142155</v>
       </c>
       <c r="O36">
-        <v>92.97426661600001</v>
+        <v>92.37598034</v>
       </c>
       <c r="P36">
-        <v>239.076685584</v>
+        <v>237.5382351599999</v>
       </c>
       <c r="Q36">
-        <v>344.376685584</v>
+        <v>342.83823516</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1004480586576118</v>
+        <v>0.1011170820241608</v>
       </c>
       <c r="T36">
-        <v>1.262079876619209</v>
+        <v>1.277530762682697</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.570616714951631</v>
+        <v>5.411456237381582</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07966170331570449</v>
+        <v>0.07949024791738524</v>
       </c>
       <c r="C37">
-        <v>2123.460815480068</v>
+        <v>2101.546995081641</v>
       </c>
       <c r="D37">
-        <v>3286.425815480068</v>
+        <v>3303.150995081642</v>
       </c>
       <c r="E37">
-        <v>-805.9349999999999</v>
+        <v>-767.296</v>
       </c>
       <c r="F37">
-        <v>1352.365</v>
+        <v>1391.004</v>
       </c>
       <c r="G37">
         <v>189.4</v>
@@ -4449,28 +4449,28 @@
         <v>404.7</v>
       </c>
       <c r="M37">
-        <v>74.78578450000002</v>
+        <v>76.92252120000001</v>
       </c>
       <c r="N37">
-        <v>329.9142155</v>
+        <v>327.7774788</v>
       </c>
       <c r="O37">
-        <v>92.37598034</v>
+        <v>91.777694064</v>
       </c>
       <c r="P37">
-        <v>237.5382351599999</v>
+        <v>235.999784736</v>
       </c>
       <c r="Q37">
-        <v>342.83823516</v>
+        <v>341.299784736</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1011170820241608</v>
+        <v>0.1018070123709144</v>
       </c>
       <c r="T37">
-        <v>1.277530762682697</v>
+        <v>1.293464488935668</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.411456237381582</v>
+        <v>5.261138008565428</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07949024791738524</v>
+        <v>0.07931879251906597</v>
       </c>
       <c r="C38">
-        <v>2101.546995081642</v>
+        <v>2079.804280031294</v>
       </c>
       <c r="D38">
-        <v>3303.150995081642</v>
+        <v>3320.047280031294</v>
       </c>
       <c r="E38">
-        <v>-767.2960000000003</v>
+        <v>-728.6570000000002</v>
       </c>
       <c r="F38">
-        <v>1391.004</v>
+        <v>1429.643</v>
       </c>
       <c r="G38">
         <v>189.4</v>
@@ -4531,28 +4531,28 @@
         <v>404.7</v>
       </c>
       <c r="M38">
-        <v>76.92252119999999</v>
+        <v>79.05925790000001</v>
       </c>
       <c r="N38">
-        <v>327.7774788</v>
+        <v>325.6407421</v>
       </c>
       <c r="O38">
-        <v>91.777694064</v>
+        <v>91.17940778800001</v>
       </c>
       <c r="P38">
-        <v>235.999784736</v>
+        <v>234.461334312</v>
       </c>
       <c r="Q38">
-        <v>341.299784736</v>
+        <v>339.761334312</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1018070123709144</v>
+        <v>0.1025188452683587</v>
       </c>
       <c r="T38">
-        <v>1.293464488935668</v>
+        <v>1.309904047768099</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.261138008565429</v>
+        <v>5.118945089415012</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07931879251906597</v>
+        <v>0.07914733712074673</v>
       </c>
       <c r="C39">
-        <v>2079.804280031294</v>
+        <v>2058.235309544455</v>
       </c>
       <c r="D39">
-        <v>3320.047280031294</v>
+        <v>3337.117309544455</v>
       </c>
       <c r="E39">
-        <v>-728.6570000000002</v>
+        <v>-690.018</v>
       </c>
       <c r="F39">
-        <v>1429.643</v>
+        <v>1468.282</v>
       </c>
       <c r="G39">
         <v>189.4</v>
@@ -4613,28 +4613,28 @@
         <v>404.7</v>
       </c>
       <c r="M39">
-        <v>79.05925790000001</v>
+        <v>81.19599460000001</v>
       </c>
       <c r="N39">
-        <v>325.6407421</v>
+        <v>323.5040054</v>
       </c>
       <c r="O39">
-        <v>91.17940778800001</v>
+        <v>90.58112151200001</v>
       </c>
       <c r="P39">
-        <v>234.461334312</v>
+        <v>232.922883888</v>
       </c>
       <c r="Q39">
-        <v>339.761334312</v>
+        <v>338.222883888</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1025188452683587</v>
+        <v>0.1032536405173334</v>
       </c>
       <c r="T39">
-        <v>1.309904047768099</v>
+        <v>1.326873914949964</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.118945089415012</v>
+        <v>4.984236008114617</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07914733712074673</v>
+        <v>0.07897588172242745</v>
       </c>
       <c r="C40">
-        <v>2058.235309544455</v>
+        <v>2036.842777395204</v>
       </c>
       <c r="D40">
-        <v>3337.117309544455</v>
+        <v>3354.363777395204</v>
       </c>
       <c r="E40">
-        <v>-690.018</v>
+        <v>-651.3790000000001</v>
       </c>
       <c r="F40">
-        <v>1468.282</v>
+        <v>1506.921</v>
       </c>
       <c r="G40">
         <v>189.4</v>
@@ -4695,28 +4695,28 @@
         <v>404.7</v>
       </c>
       <c r="M40">
-        <v>81.19599460000001</v>
+        <v>83.33273130000001</v>
       </c>
       <c r="N40">
-        <v>323.5040054</v>
+        <v>321.3672687</v>
       </c>
       <c r="O40">
-        <v>90.58112151200001</v>
+        <v>89.982835236</v>
       </c>
       <c r="P40">
-        <v>232.922883888</v>
+        <v>231.384433464</v>
       </c>
       <c r="Q40">
-        <v>338.222883888</v>
+        <v>336.684433464</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1032536405173334</v>
+        <v>0.1040125274138155</v>
       </c>
       <c r="T40">
-        <v>1.326873914949964</v>
+        <v>1.344400171219758</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.984236008114617</v>
+        <v>4.856435084829625</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07897588172242745</v>
+        <v>0.0788044263241082</v>
       </c>
       <c r="C41">
-        <v>2036.842777395204</v>
+        <v>2015.629433333386</v>
       </c>
       <c r="D41">
-        <v>3354.363777395204</v>
+        <v>3371.789433333386</v>
       </c>
       <c r="E41">
-        <v>-651.3790000000001</v>
+        <v>-612.74</v>
       </c>
       <c r="F41">
-        <v>1506.921</v>
+        <v>1545.56</v>
       </c>
       <c r="G41">
         <v>189.4</v>
@@ -4777,28 +4777,28 @@
         <v>404.7</v>
       </c>
       <c r="M41">
-        <v>83.33273130000001</v>
+        <v>85.46946800000001</v>
       </c>
       <c r="N41">
-        <v>321.3672687</v>
+        <v>319.230532</v>
       </c>
       <c r="O41">
-        <v>89.982835236</v>
+        <v>89.38454896</v>
       </c>
       <c r="P41">
-        <v>231.384433464</v>
+        <v>229.84598304</v>
       </c>
       <c r="Q41">
-        <v>336.684433464</v>
+        <v>335.14598304</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1040125274138155</v>
+        <v>0.1047967105401803</v>
       </c>
       <c r="T41">
-        <v>1.344400171219758</v>
+        <v>1.362510636031878</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.856435084829625</v>
+        <v>4.735024207708886</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0788044263241082</v>
+        <v>0.07863297092578894</v>
       </c>
       <c r="C42">
-        <v>2015.629433333386</v>
+        <v>1994.598084546171</v>
       </c>
       <c r="D42">
-        <v>3371.789433333386</v>
+        <v>3389.397084546171</v>
       </c>
       <c r="E42">
-        <v>-612.74</v>
+        <v>-574.1010000000001</v>
       </c>
       <c r="F42">
-        <v>1545.56</v>
+        <v>1584.199</v>
       </c>
       <c r="G42">
         <v>189.4</v>
@@ -4859,28 +4859,28 @@
         <v>404.7</v>
       </c>
       <c r="M42">
-        <v>85.46946800000001</v>
+        <v>87.60620470000001</v>
       </c>
       <c r="N42">
-        <v>319.230532</v>
+        <v>317.0937953</v>
       </c>
       <c r="O42">
-        <v>89.38454896</v>
+        <v>88.78626268400001</v>
       </c>
       <c r="P42">
-        <v>229.84598304</v>
+        <v>228.307532616</v>
       </c>
       <c r="Q42">
-        <v>335.14598304</v>
+        <v>333.607532616</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1047967105401803</v>
+        <v>0.105607476145405</v>
       </c>
       <c r="T42">
-        <v>1.362510636031878</v>
+        <v>1.381235014905427</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.735024207708886</v>
+        <v>4.619535812398913</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07863297092578894</v>
+        <v>0.07846151552746967</v>
       </c>
       <c r="C43">
-        <v>1994.598084546171</v>
+        <v>1973.751597165626</v>
       </c>
       <c r="D43">
-        <v>3389.397084546171</v>
+        <v>3407.189597165626</v>
       </c>
       <c r="E43">
-        <v>-574.1010000000001</v>
+        <v>-535.462</v>
       </c>
       <c r="F43">
-        <v>1584.199</v>
+        <v>1622.838</v>
       </c>
       <c r="G43">
         <v>189.4</v>
@@ -4941,28 +4941,28 @@
         <v>404.7</v>
       </c>
       <c r="M43">
-        <v>87.60620470000001</v>
+        <v>89.74294140000002</v>
       </c>
       <c r="N43">
-        <v>317.0937953</v>
+        <v>314.9570586</v>
       </c>
       <c r="O43">
-        <v>88.78626268400001</v>
+        <v>88.187976408</v>
       </c>
       <c r="P43">
-        <v>228.307532616</v>
+        <v>226.769082192</v>
       </c>
       <c r="Q43">
-        <v>333.607532616</v>
+        <v>332.069082192</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.105607476145405</v>
+        <v>0.1064461991852926</v>
       </c>
       <c r="T43">
-        <v>1.381235014905427</v>
+        <v>1.400605062015994</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.619535812398913</v>
+        <v>4.509546864484653</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07846151552746969</v>
+        <v>0.07906406012915042</v>
       </c>
       <c r="C44">
-        <v>1973.751597165625</v>
+        <v>1873.394824569495</v>
       </c>
       <c r="D44">
-        <v>3407.189597165625</v>
+        <v>3345.471824569495</v>
       </c>
       <c r="E44">
-        <v>-535.4620000000002</v>
+        <v>-496.8230000000001</v>
       </c>
       <c r="F44">
-        <v>1622.838</v>
+        <v>1661.477</v>
       </c>
       <c r="G44">
         <v>189.4</v>
@@ -5023,45 +5023,45 @@
         <v>404.7</v>
       </c>
       <c r="M44">
-        <v>89.74294140000001</v>
+        <v>96.03337060000001</v>
       </c>
       <c r="N44">
-        <v>314.9570586</v>
+        <v>308.6666294</v>
       </c>
       <c r="O44">
-        <v>88.187976408</v>
+        <v>86.426656232</v>
       </c>
       <c r="P44">
-        <v>226.769082192</v>
+        <v>222.239973168</v>
       </c>
       <c r="Q44">
-        <v>332.069082192</v>
+        <v>327.539973168</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1064461991852926</v>
+        <v>0.1073143511037727</v>
       </c>
       <c r="T44">
-        <v>1.400605062015994</v>
+        <v>1.420654759902371</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.28</v>
       </c>
       <c r="W44">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.509546864484653</v>
+        <v>4.214160114046855</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07906406012915042</v>
+        <v>0.07891060473083117</v>
       </c>
       <c r="C45">
-        <v>1873.394824569495</v>
+        <v>1850.26084827953</v>
       </c>
       <c r="D45">
-        <v>3345.471824569495</v>
+        <v>3360.97684827953</v>
       </c>
       <c r="E45">
-        <v>-496.8230000000001</v>
+        <v>-458.1840000000002</v>
       </c>
       <c r="F45">
-        <v>1661.477</v>
+        <v>1700.116</v>
       </c>
       <c r="G45">
         <v>189.4</v>
@@ -5105,28 +5105,28 @@
         <v>404.7</v>
       </c>
       <c r="M45">
-        <v>96.03337060000001</v>
+        <v>98.2667048</v>
       </c>
       <c r="N45">
-        <v>308.6666294</v>
+        <v>306.4332952</v>
       </c>
       <c r="O45">
-        <v>86.426656232</v>
+        <v>85.801322656</v>
       </c>
       <c r="P45">
-        <v>222.239973168</v>
+        <v>220.631972544</v>
       </c>
       <c r="Q45">
-        <v>327.539973168</v>
+        <v>325.931972544</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1073143511037727</v>
+        <v>0.1082135084479128</v>
       </c>
       <c r="T45">
-        <v>1.420654759902371</v>
+        <v>1.441420518427547</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.214160114046855</v>
+        <v>4.118383747818518</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07891060473083117</v>
+        <v>0.07875714933251189</v>
       </c>
       <c r="C46">
-        <v>1850.26084827953</v>
+        <v>1827.271261273081</v>
       </c>
       <c r="D46">
-        <v>3360.97684827953</v>
+        <v>3376.626261273081</v>
       </c>
       <c r="E46">
-        <v>-458.1840000000002</v>
+        <v>-419.5450000000001</v>
       </c>
       <c r="F46">
-        <v>1700.116</v>
+        <v>1738.755</v>
       </c>
       <c r="G46">
         <v>189.4</v>
@@ -5187,28 +5187,28 @@
         <v>404.7</v>
       </c>
       <c r="M46">
-        <v>98.2667048</v>
+        <v>100.500039</v>
       </c>
       <c r="N46">
-        <v>306.4332952</v>
+        <v>304.199961</v>
       </c>
       <c r="O46">
-        <v>85.801322656</v>
+        <v>85.17598907999999</v>
       </c>
       <c r="P46">
-        <v>220.631972544</v>
+        <v>219.02397192</v>
       </c>
       <c r="Q46">
-        <v>325.931972544</v>
+        <v>324.32397192</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1082135084479128</v>
+        <v>0.1091453624227489</v>
       </c>
       <c r="T46">
-        <v>1.441420518427547</v>
+        <v>1.462941395444547</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.118383747818518</v>
+        <v>4.026864108978106</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07875714933251189</v>
+        <v>0.07976289393419263</v>
       </c>
       <c r="C47">
-        <v>1827.271261273081</v>
+        <v>1688.640086261463</v>
       </c>
       <c r="D47">
-        <v>3376.626261273081</v>
+        <v>3276.634086261463</v>
       </c>
       <c r="E47">
-        <v>-419.5450000000001</v>
+        <v>-380.9060000000002</v>
       </c>
       <c r="F47">
-        <v>1738.755</v>
+        <v>1777.394</v>
       </c>
       <c r="G47">
         <v>189.4</v>
@@ -5269,45 +5269,45 @@
         <v>404.7</v>
       </c>
       <c r="M47">
-        <v>100.500039</v>
+        <v>108.9542522</v>
       </c>
       <c r="N47">
-        <v>304.199961</v>
+        <v>295.7457478</v>
       </c>
       <c r="O47">
-        <v>85.17598907999999</v>
+        <v>82.80880938400001</v>
       </c>
       <c r="P47">
-        <v>219.02397192</v>
+        <v>212.936938416</v>
       </c>
       <c r="Q47">
-        <v>324.32397192</v>
+        <v>318.236938416</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1091453624227489</v>
+        <v>0.1101117295077641</v>
       </c>
       <c r="T47">
-        <v>1.462941395444547</v>
+        <v>1.485259341980696</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.28</v>
       </c>
       <c r="W47">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.026864108978106</v>
+        <v>3.714402988670138</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07976289393419263</v>
+        <v>0.07963463853587338</v>
       </c>
       <c r="C48">
-        <v>1688.640086261463</v>
+        <v>1662.421671438819</v>
       </c>
       <c r="D48">
-        <v>3276.634086261463</v>
+        <v>3289.054671438819</v>
       </c>
       <c r="E48">
-        <v>-380.9060000000002</v>
+        <v>-342.2670000000001</v>
       </c>
       <c r="F48">
-        <v>1777.394</v>
+        <v>1816.033</v>
       </c>
       <c r="G48">
         <v>189.4</v>
@@ -5351,28 +5351,28 @@
         <v>404.7</v>
       </c>
       <c r="M48">
-        <v>108.9542522</v>
+        <v>111.3228229</v>
       </c>
       <c r="N48">
-        <v>295.7457478</v>
+        <v>293.3771771</v>
       </c>
       <c r="O48">
-        <v>82.80880938400001</v>
+        <v>82.145609588</v>
       </c>
       <c r="P48">
-        <v>212.936938416</v>
+        <v>211.231567512</v>
       </c>
       <c r="Q48">
-        <v>318.236938416</v>
+        <v>316.531567512</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1101117295077641</v>
+        <v>0.1111145632752328</v>
       </c>
       <c r="T48">
-        <v>1.485259341980696</v>
+        <v>1.508419475178586</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.714402988670138</v>
+        <v>3.635373137847369</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07963463853587338</v>
+        <v>0.07950638313755412</v>
       </c>
       <c r="C49">
-        <v>1662.421671438819</v>
+        <v>1636.297779193268</v>
       </c>
       <c r="D49">
-        <v>3289.054671438819</v>
+        <v>3301.569779193268</v>
       </c>
       <c r="E49">
-        <v>-342.2670000000001</v>
+        <v>-303.6279999999999</v>
       </c>
       <c r="F49">
-        <v>1816.033</v>
+        <v>1854.672</v>
       </c>
       <c r="G49">
         <v>189.4</v>
@@ -5433,28 +5433,28 @@
         <v>404.7</v>
       </c>
       <c r="M49">
-        <v>111.3228229</v>
+        <v>113.6913936</v>
       </c>
       <c r="N49">
-        <v>293.3771771</v>
+        <v>291.0086064</v>
       </c>
       <c r="O49">
-        <v>82.145609588</v>
+        <v>81.482409792</v>
       </c>
       <c r="P49">
-        <v>211.231567512</v>
+        <v>209.526196608</v>
       </c>
       <c r="Q49">
-        <v>316.531567512</v>
+        <v>314.826196608</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1111145632752328</v>
+        <v>0.1121559675722195</v>
       </c>
       <c r="T49">
-        <v>1.508419475178586</v>
+        <v>1.532470382730241</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.635373137847369</v>
+        <v>3.559636197475549</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07950638313755411</v>
+        <v>0.08036596773923485</v>
       </c>
       <c r="C50">
-        <v>1636.297779193269</v>
+        <v>1515.555521880218</v>
       </c>
       <c r="D50">
-        <v>3301.569779193269</v>
+        <v>3219.466521880218</v>
       </c>
       <c r="E50">
-        <v>-303.6280000000002</v>
+        <v>-264.9890000000003</v>
       </c>
       <c r="F50">
-        <v>1854.672</v>
+        <v>1893.311</v>
       </c>
       <c r="G50">
         <v>189.4</v>
@@ -5515,45 +5515,45 @@
         <v>404.7</v>
       </c>
       <c r="M50">
-        <v>113.6913936</v>
+        <v>121.3612351</v>
       </c>
       <c r="N50">
-        <v>291.0086064</v>
+        <v>283.3387649</v>
       </c>
       <c r="O50">
-        <v>81.482409792</v>
+        <v>79.33485417200001</v>
       </c>
       <c r="P50">
-        <v>209.526196608</v>
+        <v>204.003910728</v>
       </c>
       <c r="Q50">
-        <v>314.826196608</v>
+        <v>309.303910728</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1121559675722194</v>
+        <v>0.1132382112534017</v>
       </c>
       <c r="T50">
-        <v>1.532470382730241</v>
+        <v>1.55746446312706</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.28</v>
       </c>
       <c r="W50">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.559636197475549</v>
+        <v>3.334672720383347</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08036596773923485</v>
+        <v>0.0802578723409156</v>
       </c>
       <c r="C51">
-        <v>1515.555521880218</v>
+        <v>1487.016086723196</v>
       </c>
       <c r="D51">
-        <v>3219.466521880218</v>
+        <v>3229.566086723196</v>
       </c>
       <c r="E51">
-        <v>-264.9890000000003</v>
+        <v>-226.3500000000001</v>
       </c>
       <c r="F51">
-        <v>1893.311</v>
+        <v>1931.95</v>
       </c>
       <c r="G51">
         <v>189.4</v>
@@ -5597,28 +5597,28 @@
         <v>404.7</v>
       </c>
       <c r="M51">
-        <v>121.3612351</v>
+        <v>123.837995</v>
       </c>
       <c r="N51">
-        <v>283.3387649</v>
+        <v>280.862005</v>
       </c>
       <c r="O51">
-        <v>79.33485417200001</v>
+        <v>78.64136139999999</v>
       </c>
       <c r="P51">
-        <v>204.003910728</v>
+        <v>202.2206436</v>
       </c>
       <c r="Q51">
-        <v>309.303910728</v>
+        <v>307.5206436</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1132382112534017</v>
+        <v>0.1143637446818312</v>
       </c>
       <c r="T51">
-        <v>1.55746446312706</v>
+        <v>1.583458306739751</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.334672720383347</v>
+        <v>3.26797926597568</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0802578723409156</v>
+        <v>0.08014977694259634</v>
       </c>
       <c r="C52">
-        <v>1487.016086723196</v>
+        <v>1458.540216257519</v>
       </c>
       <c r="D52">
-        <v>3229.566086723196</v>
+        <v>3239.72921625752</v>
       </c>
       <c r="E52">
-        <v>-226.3500000000001</v>
+        <v>-187.711</v>
       </c>
       <c r="F52">
-        <v>1931.95</v>
+        <v>1970.589</v>
       </c>
       <c r="G52">
         <v>189.4</v>
@@ -5679,28 +5679,28 @@
         <v>404.7</v>
       </c>
       <c r="M52">
-        <v>123.837995</v>
+        <v>126.3147549</v>
       </c>
       <c r="N52">
-        <v>280.862005</v>
+        <v>278.3852451</v>
       </c>
       <c r="O52">
-        <v>78.64136139999999</v>
+        <v>77.94786862799999</v>
       </c>
       <c r="P52">
-        <v>202.2206436</v>
+        <v>200.437376472</v>
       </c>
       <c r="Q52">
-        <v>307.5206436</v>
+        <v>305.737376472</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1143637446818312</v>
+        <v>0.1155352182501966</v>
       </c>
       <c r="T52">
-        <v>1.583458306739751</v>
+        <v>1.610513123561123</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.26797926597568</v>
+        <v>3.203901241152627</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08014977694259634</v>
+        <v>0.08004168154427707</v>
       </c>
       <c r="C53">
-        <v>1458.540216257519</v>
+        <v>1430.128512473247</v>
       </c>
       <c r="D53">
-        <v>3239.72921625752</v>
+        <v>3249.956512473247</v>
       </c>
       <c r="E53">
-        <v>-187.711</v>
+        <v>-149.0720000000001</v>
       </c>
       <c r="F53">
-        <v>1970.589</v>
+        <v>2009.228</v>
       </c>
       <c r="G53">
         <v>189.4</v>
@@ -5761,28 +5761,28 @@
         <v>404.7</v>
       </c>
       <c r="M53">
-        <v>126.3147549</v>
+        <v>128.7915148</v>
       </c>
       <c r="N53">
-        <v>278.3852451</v>
+        <v>275.9084852</v>
       </c>
       <c r="O53">
-        <v>77.94786862799999</v>
+        <v>77.254375856</v>
       </c>
       <c r="P53">
-        <v>200.437376472</v>
+        <v>198.654109344</v>
       </c>
       <c r="Q53">
-        <v>305.737376472</v>
+        <v>303.954109344</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1155352182501966</v>
+        <v>0.1167555032172439</v>
       </c>
       <c r="T53">
-        <v>1.610513123561123</v>
+        <v>1.638695224416719</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.203901241152627</v>
+        <v>3.142287755745846</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08004168154427707</v>
+        <v>0.07993358614595782</v>
       </c>
       <c r="C54">
-        <v>1430.128512473247</v>
+        <v>1401.781584986045</v>
       </c>
       <c r="D54">
-        <v>3249.956512473247</v>
+        <v>3260.248584986045</v>
       </c>
       <c r="E54">
-        <v>-149.0720000000001</v>
+        <v>-110.433</v>
       </c>
       <c r="F54">
-        <v>2009.228</v>
+        <v>2047.867</v>
       </c>
       <c r="G54">
         <v>189.4</v>
@@ -5843,28 +5843,28 @@
         <v>404.7</v>
       </c>
       <c r="M54">
-        <v>128.7915148</v>
+        <v>131.2682747</v>
       </c>
       <c r="N54">
-        <v>275.9084852</v>
+        <v>273.4317252999999</v>
       </c>
       <c r="O54">
-        <v>77.254375856</v>
+        <v>76.56088308399998</v>
       </c>
       <c r="P54">
-        <v>198.654109344</v>
+        <v>196.8708422159999</v>
       </c>
       <c r="Q54">
-        <v>303.954109344</v>
+        <v>302.170842216</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1167555032172439</v>
+        <v>0.1180277152041656</v>
       </c>
       <c r="T54">
-        <v>1.638695224416719</v>
+        <v>1.668076563606595</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.142287755745846</v>
+        <v>3.082999307524226</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07993358614595782</v>
+        <v>0.07982549074763856</v>
       </c>
       <c r="C55">
-        <v>1401.781584986045</v>
+        <v>1373.500051158324</v>
       </c>
       <c r="D55">
-        <v>3260.248584986045</v>
+        <v>3270.606051158324</v>
       </c>
       <c r="E55">
-        <v>-110.433</v>
+        <v>-71.79399999999987</v>
       </c>
       <c r="F55">
-        <v>2047.867</v>
+        <v>2086.506</v>
       </c>
       <c r="G55">
         <v>189.4</v>
@@ -5925,28 +5925,28 @@
         <v>404.7</v>
       </c>
       <c r="M55">
-        <v>131.2682747</v>
+        <v>133.7450346</v>
       </c>
       <c r="N55">
-        <v>273.4317252999999</v>
+        <v>270.9549654</v>
       </c>
       <c r="O55">
-        <v>76.56088308399998</v>
+        <v>75.86739031200001</v>
       </c>
       <c r="P55">
-        <v>196.8708422159999</v>
+        <v>195.087575088</v>
       </c>
       <c r="Q55">
-        <v>302.170842216</v>
+        <v>300.387575088</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1180277152041656</v>
+        <v>0.119355240755736</v>
       </c>
       <c r="T55">
-        <v>1.668076563606595</v>
+        <v>1.698735352326467</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.082999307524226</v>
+        <v>3.025906727755259</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07982549074763856</v>
+        <v>0.08280619534931929</v>
       </c>
       <c r="C56">
-        <v>1373.500051158324</v>
+        <v>1071.42649878271</v>
       </c>
       <c r="D56">
-        <v>3270.606051158324</v>
+        <v>3007.17149878271</v>
       </c>
       <c r="E56">
-        <v>-71.79399999999987</v>
+        <v>-33.15499999999975</v>
       </c>
       <c r="F56">
-        <v>2086.506</v>
+        <v>2125.145</v>
       </c>
       <c r="G56">
         <v>189.4</v>
@@ -6007,45 +6007,45 @@
         <v>404.7</v>
       </c>
       <c r="M56">
-        <v>133.7450346</v>
+        <v>152.7979255</v>
       </c>
       <c r="N56">
-        <v>270.9549654</v>
+        <v>251.9020744999999</v>
       </c>
       <c r="O56">
-        <v>75.86739031200001</v>
+        <v>70.53258086</v>
       </c>
       <c r="P56">
-        <v>195.087575088</v>
+        <v>181.3694936399999</v>
       </c>
       <c r="Q56">
-        <v>300.387575088</v>
+        <v>286.6694936399999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.119355240755736</v>
+        <v>0.1207417674429318</v>
       </c>
       <c r="T56">
-        <v>1.698735352326467</v>
+        <v>1.730756753878332</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.28</v>
       </c>
       <c r="W56">
-        <v>0.046152</v>
+        <v>0.051768</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.025906727755259</v>
+        <v>2.648596168277166</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08280619534931929</v>
+        <v>0.08275425995100004</v>
       </c>
       <c r="C57">
-        <v>1071.42649878271</v>
+        <v>1037.013767954672</v>
       </c>
       <c r="D57">
-        <v>3007.17149878271</v>
+        <v>3011.397767954672</v>
       </c>
       <c r="E57">
-        <v>-33.15499999999975</v>
+        <v>5.483999999999924</v>
       </c>
       <c r="F57">
-        <v>2125.145</v>
+        <v>2163.784</v>
       </c>
       <c r="G57">
         <v>189.4</v>
@@ -6089,28 +6089,28 @@
         <v>404.7</v>
       </c>
       <c r="M57">
-        <v>152.7979255</v>
+        <v>155.5760696</v>
       </c>
       <c r="N57">
-        <v>251.9020744999999</v>
+        <v>249.1239304</v>
       </c>
       <c r="O57">
-        <v>70.53258086</v>
+        <v>69.754700512</v>
       </c>
       <c r="P57">
-        <v>181.3694936399999</v>
+        <v>179.369229888</v>
       </c>
       <c r="Q57">
-        <v>286.6694936399999</v>
+        <v>284.669229888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1207417674429318</v>
+        <v>0.1221913180704546</v>
       </c>
       <c r="T57">
-        <v>1.730756753878332</v>
+        <v>1.764233673682555</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.648596168277166</v>
+        <v>2.60129980812936</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08275425995100004</v>
+        <v>0.08270232455268078</v>
       </c>
       <c r="C58">
-        <v>1037.013767954672</v>
+        <v>1002.612933015336</v>
       </c>
       <c r="D58">
-        <v>3011.397767954672</v>
+        <v>3015.635933015336</v>
       </c>
       <c r="E58">
-        <v>5.483999999999924</v>
+        <v>44.12300000000005</v>
       </c>
       <c r="F58">
-        <v>2163.784</v>
+        <v>2202.423</v>
       </c>
       <c r="G58">
         <v>189.4</v>
@@ -6171,28 +6171,28 @@
         <v>404.7</v>
       </c>
       <c r="M58">
-        <v>155.5760696</v>
+        <v>158.3542137</v>
       </c>
       <c r="N58">
-        <v>249.1239304</v>
+        <v>246.3457863</v>
       </c>
       <c r="O58">
-        <v>69.754700512</v>
+        <v>68.97682016399999</v>
       </c>
       <c r="P58">
-        <v>179.369229888</v>
+        <v>177.368966136</v>
       </c>
       <c r="Q58">
-        <v>284.669229888</v>
+        <v>282.668966136</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1221913180704546</v>
+        <v>0.1237082896573972</v>
       </c>
       <c r="T58">
-        <v>1.764233673682555</v>
+        <v>1.799267659524184</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.60129980812936</v>
+        <v>2.555662969390248</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08270232455268078</v>
+        <v>0.08265038915436151</v>
       </c>
       <c r="C59">
-        <v>1002.612933015336</v>
+        <v>968.2240442614066</v>
       </c>
       <c r="D59">
-        <v>3015.635933015336</v>
+        <v>3019.886044261407</v>
       </c>
       <c r="E59">
-        <v>44.12300000000005</v>
+        <v>82.76200000000017</v>
       </c>
       <c r="F59">
-        <v>2202.423</v>
+        <v>2241.062</v>
       </c>
       <c r="G59">
         <v>189.4</v>
@@ -6253,28 +6253,28 @@
         <v>404.7</v>
       </c>
       <c r="M59">
-        <v>158.3542137</v>
+        <v>161.1323578000001</v>
       </c>
       <c r="N59">
-        <v>246.3457863</v>
+        <v>243.5676421999999</v>
       </c>
       <c r="O59">
-        <v>68.97682016399999</v>
+        <v>68.19893981599999</v>
       </c>
       <c r="P59">
-        <v>177.368966136</v>
+        <v>175.368702384</v>
       </c>
       <c r="Q59">
-        <v>282.668966136</v>
+        <v>280.668702384</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1237082896573972</v>
+        <v>0.1252974979865751</v>
       </c>
       <c r="T59">
-        <v>1.799267659524184</v>
+        <v>1.835969930405891</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.555662969390248</v>
+        <v>2.511599814745589</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08265038915436151</v>
+        <v>0.08425517375604227</v>
       </c>
       <c r="C60">
-        <v>968.224044261407</v>
+        <v>803.561257360695</v>
       </c>
       <c r="D60">
-        <v>3019.886044261407</v>
+        <v>2893.862257360695</v>
       </c>
       <c r="E60">
-        <v>82.76199999999972</v>
+        <v>121.4009999999998</v>
       </c>
       <c r="F60">
-        <v>2241.062</v>
+        <v>2279.701</v>
       </c>
       <c r="G60">
         <v>189.4</v>
@@ -6335,45 +6335,45 @@
         <v>404.7</v>
       </c>
       <c r="M60">
-        <v>161.1323578</v>
+        <v>172.8013358</v>
       </c>
       <c r="N60">
-        <v>243.5676422</v>
+        <v>231.8986642</v>
       </c>
       <c r="O60">
-        <v>68.19893981600001</v>
+        <v>64.93162597600001</v>
       </c>
       <c r="P60">
-        <v>175.368702384</v>
+        <v>166.967038224</v>
       </c>
       <c r="Q60">
-        <v>280.668702384</v>
+        <v>272.267038224</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.125297497986575</v>
+        <v>0.1269642286732738</v>
       </c>
       <c r="T60">
-        <v>1.83596993040589</v>
+        <v>1.874462555964753</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.28</v>
       </c>
       <c r="W60">
-        <v>0.051768</v>
+        <v>0.054576</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.51159981474559</v>
+        <v>2.341995784502494</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08425517375604227</v>
+        <v>0.084231318357723</v>
       </c>
       <c r="C61">
-        <v>803.561257360695</v>
+        <v>766.7185589131909</v>
       </c>
       <c r="D61">
-        <v>2893.862257360695</v>
+        <v>2895.658558913191</v>
       </c>
       <c r="E61">
-        <v>121.4009999999998</v>
+        <v>160.04</v>
       </c>
       <c r="F61">
-        <v>2279.701</v>
+        <v>2318.34</v>
       </c>
       <c r="G61">
         <v>189.4</v>
@@ -6417,28 +6417,28 @@
         <v>404.7</v>
       </c>
       <c r="M61">
-        <v>172.8013358</v>
+        <v>175.730172</v>
       </c>
       <c r="N61">
-        <v>231.8986642</v>
+        <v>228.9698279999999</v>
       </c>
       <c r="O61">
-        <v>64.93162597600001</v>
+        <v>64.11155183999999</v>
       </c>
       <c r="P61">
-        <v>166.967038224</v>
+        <v>164.8582761599999</v>
       </c>
       <c r="Q61">
-        <v>272.267038224</v>
+        <v>270.15827616</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1269642286732738</v>
+        <v>0.1287142958943075</v>
       </c>
       <c r="T61">
-        <v>1.874462555964753</v>
+        <v>1.914879812801559</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.341995784502494</v>
+        <v>2.302962521427452</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.084231318357723</v>
+        <v>0.08420746295940373</v>
       </c>
       <c r="C62">
-        <v>766.7185589131909</v>
+        <v>729.8780918804036</v>
       </c>
       <c r="D62">
-        <v>2895.658558913191</v>
+        <v>2897.457091880403</v>
       </c>
       <c r="E62">
-        <v>160.04</v>
+        <v>198.6789999999996</v>
       </c>
       <c r="F62">
-        <v>2318.34</v>
+        <v>2356.979</v>
       </c>
       <c r="G62">
         <v>189.4</v>
@@ -6499,28 +6499,28 @@
         <v>404.7</v>
       </c>
       <c r="M62">
-        <v>175.730172</v>
+        <v>178.6590082</v>
       </c>
       <c r="N62">
-        <v>228.9698279999999</v>
+        <v>226.0409918</v>
       </c>
       <c r="O62">
-        <v>64.11155183999999</v>
+        <v>63.29147770400001</v>
       </c>
       <c r="P62">
-        <v>164.8582761599999</v>
+        <v>162.749514096</v>
       </c>
       <c r="Q62">
-        <v>270.15827616</v>
+        <v>268.049514096</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1287142958943075</v>
+        <v>0.1305541101523173</v>
       </c>
       <c r="T62">
-        <v>1.914879812801559</v>
+        <v>1.95736974947615</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.302962521427452</v>
+        <v>2.265209037469626</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08420746295940373</v>
+        <v>0.08418360756108448</v>
       </c>
       <c r="C63">
-        <v>729.8780918804036</v>
+        <v>693.0398604228017</v>
       </c>
       <c r="D63">
-        <v>2897.457091880403</v>
+        <v>2899.257860422802</v>
       </c>
       <c r="E63">
-        <v>198.6789999999996</v>
+        <v>237.3179999999998</v>
       </c>
       <c r="F63">
-        <v>2356.979</v>
+        <v>2395.618</v>
       </c>
       <c r="G63">
         <v>189.4</v>
@@ -6581,28 +6581,28 @@
         <v>404.7</v>
       </c>
       <c r="M63">
-        <v>178.6590082</v>
+        <v>181.5878444</v>
       </c>
       <c r="N63">
-        <v>226.0409918</v>
+        <v>223.1121556</v>
       </c>
       <c r="O63">
-        <v>63.29147770400001</v>
+        <v>62.471403568</v>
       </c>
       <c r="P63">
-        <v>162.749514096</v>
+        <v>160.640752032</v>
       </c>
       <c r="Q63">
-        <v>268.049514096</v>
+        <v>265.940752032</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1305541101523173</v>
+        <v>0.132490756739696</v>
       </c>
       <c r="T63">
-        <v>1.95736974947615</v>
+        <v>2.002095998607297</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.265209037469626</v>
+        <v>2.228673407833019</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08418360756108448</v>
+        <v>0.08415975216276521</v>
       </c>
       <c r="C64">
-        <v>693.0398604228017</v>
+        <v>656.2038687112072</v>
       </c>
       <c r="D64">
-        <v>2899.257860422802</v>
+        <v>2901.060868711207</v>
       </c>
       <c r="E64">
-        <v>237.3179999999998</v>
+        <v>275.9569999999999</v>
       </c>
       <c r="F64">
-        <v>2395.618</v>
+        <v>2434.257</v>
       </c>
       <c r="G64">
         <v>189.4</v>
@@ -6663,28 +6663,28 @@
         <v>404.7</v>
       </c>
       <c r="M64">
-        <v>181.5878444</v>
+        <v>184.5166806</v>
       </c>
       <c r="N64">
-        <v>223.1121556</v>
+        <v>220.1833194</v>
       </c>
       <c r="O64">
-        <v>62.471403568</v>
+        <v>61.651329432</v>
       </c>
       <c r="P64">
-        <v>160.640752032</v>
+        <v>158.5319899679999</v>
       </c>
       <c r="Q64">
-        <v>265.940752032</v>
+        <v>263.831989968</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.132490756739696</v>
+        <v>0.1345320869263925</v>
       </c>
       <c r="T64">
-        <v>2.002095998607297</v>
+        <v>2.049239882826616</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.228673407833019</v>
+        <v>2.193297639454717</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08415975216276521</v>
+        <v>0.08413589676444597</v>
       </c>
       <c r="C65">
-        <v>656.2038687112072</v>
+        <v>619.3701209268183</v>
       </c>
       <c r="D65">
-        <v>2901.060868711207</v>
+        <v>2902.866120926818</v>
       </c>
       <c r="E65">
-        <v>275.9569999999999</v>
+        <v>314.596</v>
       </c>
       <c r="F65">
-        <v>2434.257</v>
+        <v>2472.896</v>
       </c>
       <c r="G65">
         <v>189.4</v>
@@ -6745,28 +6745,28 @@
         <v>404.7</v>
       </c>
       <c r="M65">
-        <v>184.5166806</v>
+        <v>187.4455168</v>
       </c>
       <c r="N65">
-        <v>220.1833194</v>
+        <v>217.2544832</v>
       </c>
       <c r="O65">
-        <v>61.651329432</v>
+        <v>60.83125529599999</v>
       </c>
       <c r="P65">
-        <v>158.5319899679999</v>
+        <v>156.423227904</v>
       </c>
       <c r="Q65">
-        <v>263.831989968</v>
+        <v>261.7232279039999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1345320869263925</v>
+        <v>0.1366868243456832</v>
       </c>
       <c r="T65">
-        <v>2.049239882826616</v>
+        <v>2.099002871724786</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.193297639454717</v>
+        <v>2.159027363838237</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08413589676444597</v>
+        <v>0.0841120413661267</v>
       </c>
       <c r="C66">
-        <v>619.3701209268183</v>
+        <v>582.5386212612552</v>
       </c>
       <c r="D66">
-        <v>2902.866120926818</v>
+        <v>2904.673621261255</v>
       </c>
       <c r="E66">
-        <v>314.596</v>
+        <v>353.2350000000001</v>
       </c>
       <c r="F66">
-        <v>2472.896</v>
+        <v>2511.535</v>
       </c>
       <c r="G66">
         <v>189.4</v>
@@ -6827,28 +6827,28 @@
         <v>404.7</v>
       </c>
       <c r="M66">
-        <v>187.4455168</v>
+        <v>190.374353</v>
       </c>
       <c r="N66">
-        <v>217.2544832</v>
+        <v>214.3256469999999</v>
       </c>
       <c r="O66">
-        <v>60.83125529599999</v>
+        <v>60.01118115999999</v>
       </c>
       <c r="P66">
-        <v>156.423227904</v>
+        <v>154.31446584</v>
       </c>
       <c r="Q66">
-        <v>261.7232279039999</v>
+        <v>259.61446584</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1366868243456832</v>
+        <v>0.1389646896175049</v>
       </c>
       <c r="T66">
-        <v>2.099002871724786</v>
+        <v>2.151609459988565</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.159027363838237</v>
+        <v>2.125811558240725</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0841120413661267</v>
+        <v>0.08408818596780743</v>
       </c>
       <c r="C67">
-        <v>582.5386212612552</v>
+        <v>545.7093739165766</v>
       </c>
       <c r="D67">
-        <v>2904.673621261255</v>
+        <v>2906.483373916577</v>
       </c>
       <c r="E67">
-        <v>353.2350000000001</v>
+        <v>391.8739999999998</v>
       </c>
       <c r="F67">
-        <v>2511.535</v>
+        <v>2550.174</v>
       </c>
       <c r="G67">
         <v>189.4</v>
@@ -6909,28 +6909,28 @@
         <v>404.7</v>
       </c>
       <c r="M67">
-        <v>190.374353</v>
+        <v>193.3031892</v>
       </c>
       <c r="N67">
-        <v>214.3256469999999</v>
+        <v>211.3968108</v>
       </c>
       <c r="O67">
-        <v>60.01118115999999</v>
+        <v>59.191107024</v>
       </c>
       <c r="P67">
-        <v>154.31446584</v>
+        <v>152.205703776</v>
       </c>
       <c r="Q67">
-        <v>259.61446584</v>
+        <v>257.505703776</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1389646896175049</v>
+        <v>0.1413765469641395</v>
       </c>
       <c r="T67">
-        <v>2.151609459988565</v>
+        <v>2.20731055344433</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.125811558240725</v>
+        <v>2.093602292206775</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08408818596780743</v>
+        <v>0.08406433056948817</v>
       </c>
       <c r="C68">
-        <v>545.7093739165766</v>
+        <v>508.882383105321</v>
       </c>
       <c r="D68">
-        <v>2906.483373916577</v>
+        <v>2908.295383105321</v>
       </c>
       <c r="E68">
-        <v>391.8739999999998</v>
+        <v>430.5129999999999</v>
       </c>
       <c r="F68">
-        <v>2550.174</v>
+        <v>2588.813</v>
       </c>
       <c r="G68">
         <v>189.4</v>
@@ -6991,28 +6991,28 @@
         <v>404.7</v>
       </c>
       <c r="M68">
-        <v>193.3031892</v>
+        <v>196.2320254</v>
       </c>
       <c r="N68">
-        <v>211.3968108</v>
+        <v>208.4679746</v>
       </c>
       <c r="O68">
-        <v>59.191107024</v>
+        <v>58.37103288799999</v>
       </c>
       <c r="P68">
-        <v>152.205703776</v>
+        <v>150.096941712</v>
       </c>
       <c r="Q68">
-        <v>257.505703776</v>
+        <v>255.396941712</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1413765469641395</v>
+        <v>0.1439345774832975</v>
       </c>
       <c r="T68">
-        <v>2.20731055344433</v>
+        <v>2.266387470745901</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.093602292206775</v>
+        <v>2.062354496800704</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08406433056948817</v>
+        <v>0.08404047517116892</v>
       </c>
       <c r="C69">
-        <v>508.882383105321</v>
+        <v>472.0576530505418</v>
       </c>
       <c r="D69">
-        <v>2908.295383105321</v>
+        <v>2910.109653050542</v>
       </c>
       <c r="E69">
-        <v>430.5129999999999</v>
+        <v>469.152</v>
       </c>
       <c r="F69">
-        <v>2588.813</v>
+        <v>2627.452</v>
       </c>
       <c r="G69">
         <v>189.4</v>
@@ -7073,28 +7073,28 @@
         <v>404.7</v>
       </c>
       <c r="M69">
-        <v>196.2320254</v>
+        <v>199.1608616</v>
       </c>
       <c r="N69">
-        <v>208.4679746</v>
+        <v>205.5391384</v>
       </c>
       <c r="O69">
-        <v>58.37103288799999</v>
+        <v>57.55095875199999</v>
       </c>
       <c r="P69">
-        <v>150.096941712</v>
+        <v>147.988179648</v>
       </c>
       <c r="Q69">
-        <v>255.396941712</v>
+        <v>253.288179648</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1439345774832975</v>
+        <v>0.1466524849099029</v>
       </c>
       <c r="T69">
-        <v>2.266387470745901</v>
+        <v>2.329156695378819</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.062354496800704</v>
+        <v>2.032025754200693</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08404047517116892</v>
+        <v>0.08401661977284966</v>
       </c>
       <c r="C70">
-        <v>472.0576530505418</v>
+        <v>435.2351879858361</v>
       </c>
       <c r="D70">
-        <v>2910.109653050542</v>
+        <v>2911.926187985836</v>
       </c>
       <c r="E70">
-        <v>469.152</v>
+        <v>507.7910000000002</v>
       </c>
       <c r="F70">
-        <v>2627.452</v>
+        <v>2666.091</v>
       </c>
       <c r="G70">
         <v>189.4</v>
@@ -7155,28 +7155,28 @@
         <v>404.7</v>
       </c>
       <c r="M70">
-        <v>199.1608616</v>
+        <v>202.0896978</v>
       </c>
       <c r="N70">
-        <v>205.5391384</v>
+        <v>202.6103021999999</v>
       </c>
       <c r="O70">
-        <v>57.55095875199999</v>
+        <v>56.73088461599999</v>
       </c>
       <c r="P70">
-        <v>147.988179648</v>
+        <v>145.879417584</v>
       </c>
       <c r="Q70">
-        <v>253.288179648</v>
+        <v>251.179417584</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1466524849099029</v>
+        <v>0.1495457412027408</v>
       </c>
       <c r="T70">
-        <v>2.329156695378819</v>
+        <v>2.39597554740741</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.032025754200693</v>
+        <v>2.002576105589089</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08401661977284966</v>
+        <v>0.0911495643745304</v>
       </c>
       <c r="C71">
-        <v>435.2351879858361</v>
+        <v>-61.41500726065442</v>
       </c>
       <c r="D71">
-        <v>2911.926187985836</v>
+        <v>2453.914992739346</v>
       </c>
       <c r="E71">
-        <v>507.7910000000002</v>
+        <v>546.4300000000003</v>
       </c>
       <c r="F71">
-        <v>2666.091</v>
+        <v>2704.73</v>
       </c>
       <c r="G71">
         <v>189.4</v>
@@ -7237,45 +7237,45 @@
         <v>404.7</v>
       </c>
       <c r="M71">
-        <v>202.0896978</v>
+        <v>243.4257</v>
       </c>
       <c r="N71">
-        <v>202.6103021999999</v>
+        <v>161.2743</v>
       </c>
       <c r="O71">
-        <v>56.73088461599999</v>
+        <v>45.15680399999999</v>
       </c>
       <c r="P71">
-        <v>145.879417584</v>
+        <v>116.117496</v>
       </c>
       <c r="Q71">
-        <v>251.179417584</v>
+        <v>221.417496</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1495457412027408</v>
+        <v>0.1526318812484347</v>
       </c>
       <c r="T71">
-        <v>2.39597554740741</v>
+        <v>2.46724898957124</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.28</v>
       </c>
       <c r="W71">
-        <v>0.054576</v>
+        <v>0.0648</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.002576105589089</v>
+        <v>1.662519610706675</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0911495643745304</v>
+        <v>0.09122794897621114</v>
       </c>
       <c r="C72">
-        <v>-61.41500726065442</v>
+        <v>-104.2881660461412</v>
       </c>
       <c r="D72">
-        <v>2453.914992739346</v>
+        <v>2449.680833953859</v>
       </c>
       <c r="E72">
-        <v>546.4300000000003</v>
+        <v>585.069</v>
       </c>
       <c r="F72">
-        <v>2704.73</v>
+        <v>2743.369</v>
       </c>
       <c r="G72">
         <v>189.4</v>
@@ -7319,28 +7319,28 @@
         <v>404.7</v>
       </c>
       <c r="M72">
-        <v>243.4257</v>
+        <v>246.90321</v>
       </c>
       <c r="N72">
-        <v>161.2743</v>
+        <v>157.79679</v>
       </c>
       <c r="O72">
-        <v>45.15680399999999</v>
+        <v>44.1831012</v>
       </c>
       <c r="P72">
-        <v>116.117496</v>
+        <v>113.6136888</v>
       </c>
       <c r="Q72">
-        <v>221.417496</v>
+        <v>218.9136888</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1526318812484347</v>
+        <v>0.1559308585386591</v>
       </c>
       <c r="T72">
-        <v>2.46724898957124</v>
+        <v>2.543437841539472</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.662519610706675</v>
+        <v>1.639103841541793</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09122794897621114</v>
+        <v>0.09130633357789189</v>
       </c>
       <c r="C73">
-        <v>-104.2881660461412</v>
+        <v>-147.1467381653883</v>
       </c>
       <c r="D73">
-        <v>2449.680833953859</v>
+        <v>2445.461261834611</v>
       </c>
       <c r="E73">
-        <v>585.069</v>
+        <v>623.7079999999996</v>
       </c>
       <c r="F73">
-        <v>2743.369</v>
+        <v>2782.008</v>
       </c>
       <c r="G73">
         <v>189.4</v>
@@ -7401,28 +7401,28 @@
         <v>404.7</v>
       </c>
       <c r="M73">
-        <v>246.90321</v>
+        <v>250.38072</v>
       </c>
       <c r="N73">
-        <v>157.79679</v>
+        <v>154.31928</v>
       </c>
       <c r="O73">
-        <v>44.1831012</v>
+        <v>43.20939840000001</v>
       </c>
       <c r="P73">
-        <v>113.6136888</v>
+        <v>111.1098816</v>
       </c>
       <c r="Q73">
-        <v>218.9136888</v>
+        <v>216.4098816</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1559308585386591</v>
+        <v>0.1594654770638996</v>
       </c>
       <c r="T73">
-        <v>2.543437841539471</v>
+        <v>2.625068754362577</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.639103841541793</v>
+        <v>1.616338510409268</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09130633357789189</v>
+        <v>0.09138471817957261</v>
       </c>
       <c r="C74">
-        <v>-147.1467381653883</v>
+        <v>-189.9907988653235</v>
       </c>
       <c r="D74">
-        <v>2445.461261834611</v>
+        <v>2441.256201134676</v>
       </c>
       <c r="E74">
-        <v>623.7079999999996</v>
+        <v>662.3469999999998</v>
       </c>
       <c r="F74">
-        <v>2782.008</v>
+        <v>2820.647</v>
       </c>
       <c r="G74">
         <v>189.4</v>
@@ -7483,28 +7483,28 @@
         <v>404.7</v>
       </c>
       <c r="M74">
-        <v>250.38072</v>
+        <v>253.85823</v>
       </c>
       <c r="N74">
-        <v>154.31928</v>
+        <v>150.84177</v>
       </c>
       <c r="O74">
-        <v>43.20939840000001</v>
+        <v>42.2356956</v>
       </c>
       <c r="P74">
-        <v>111.1098816</v>
+        <v>108.6060744</v>
       </c>
       <c r="Q74">
-        <v>216.4098816</v>
+        <v>213.9060744</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1594654770638996</v>
+        <v>0.1632619191836023</v>
       </c>
       <c r="T74">
-        <v>2.625068754362577</v>
+        <v>2.712746401468875</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.616338510409268</v>
+        <v>1.594196886979004</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09138471817957261</v>
+        <v>0.09146310278125334</v>
       </c>
       <c r="C75">
-        <v>-189.9907988653235</v>
+        <v>-232.820422876207</v>
       </c>
       <c r="D75">
-        <v>2441.256201134676</v>
+        <v>2437.065577123793</v>
       </c>
       <c r="E75">
-        <v>662.3469999999998</v>
+        <v>700.9859999999999</v>
       </c>
       <c r="F75">
-        <v>2820.647</v>
+        <v>2859.286</v>
       </c>
       <c r="G75">
         <v>189.4</v>
@@ -7565,28 +7565,28 @@
         <v>404.7</v>
       </c>
       <c r="M75">
-        <v>253.85823</v>
+        <v>257.33574</v>
       </c>
       <c r="N75">
-        <v>150.84177</v>
+        <v>147.36426</v>
       </c>
       <c r="O75">
-        <v>42.2356956</v>
+        <v>41.2619928</v>
       </c>
       <c r="P75">
-        <v>108.6060744</v>
+        <v>106.1022672</v>
       </c>
       <c r="Q75">
-        <v>213.9060744</v>
+        <v>211.4022672</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1632619191836023</v>
+        <v>0.1673503953125129</v>
       </c>
       <c r="T75">
-        <v>2.712746401468875</v>
+        <v>2.807168482967966</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.594196886979004</v>
+        <v>1.572653685803612</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09146310278125334</v>
+        <v>0.09154148738293409</v>
       </c>
       <c r="C76">
-        <v>-232.820422876207</v>
+        <v>-275.6356844160537</v>
       </c>
       <c r="D76">
-        <v>2437.065577123793</v>
+        <v>2432.889315583946</v>
       </c>
       <c r="E76">
-        <v>700.9859999999999</v>
+        <v>739.625</v>
       </c>
       <c r="F76">
-        <v>2859.286</v>
+        <v>2897.925</v>
       </c>
       <c r="G76">
         <v>189.4</v>
@@ -7647,28 +7647,28 @@
         <v>404.7</v>
       </c>
       <c r="M76">
-        <v>257.33574</v>
+        <v>260.81325</v>
       </c>
       <c r="N76">
-        <v>147.36426</v>
+        <v>143.88675</v>
       </c>
       <c r="O76">
-        <v>41.2619928</v>
+        <v>40.28829</v>
       </c>
       <c r="P76">
-        <v>106.1022672</v>
+        <v>103.59846</v>
       </c>
       <c r="Q76">
-        <v>211.4022672</v>
+        <v>208.89846</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1673503953125129</v>
+        <v>0.1717659495317364</v>
       </c>
       <c r="T76">
-        <v>2.807168482967966</v>
+        <v>2.909144330986984</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.572653685803612</v>
+        <v>1.551684969992897</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09154148738293409</v>
+        <v>0.09161987198461483</v>
       </c>
       <c r="C77">
-        <v>-275.6356844160537</v>
+        <v>-318.4366571950131</v>
       </c>
       <c r="D77">
-        <v>2432.889315583946</v>
+        <v>2428.727342804987</v>
       </c>
       <c r="E77">
-        <v>739.625</v>
+        <v>778.2640000000001</v>
       </c>
       <c r="F77">
-        <v>2897.925</v>
+        <v>2936.564</v>
       </c>
       <c r="G77">
         <v>189.4</v>
@@ -7729,28 +7729,28 @@
         <v>404.7</v>
       </c>
       <c r="M77">
-        <v>260.81325</v>
+        <v>264.29076</v>
       </c>
       <c r="N77">
-        <v>143.88675</v>
+        <v>140.40924</v>
       </c>
       <c r="O77">
-        <v>40.28829</v>
+        <v>39.31458719999999</v>
       </c>
       <c r="P77">
-        <v>103.59846</v>
+        <v>101.0946528</v>
       </c>
       <c r="Q77">
-        <v>208.89846</v>
+        <v>206.3946528</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1717659495317364</v>
+        <v>0.1765494666025618</v>
       </c>
       <c r="T77">
-        <v>2.909144330986984</v>
+        <v>3.01961816634092</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.551684969992897</v>
+        <v>1.53126806249299</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09161987198461483</v>
+        <v>0.09169825658629557</v>
       </c>
       <c r="C78">
-        <v>-318.4366571950131</v>
+        <v>-361.2234144197123</v>
       </c>
       <c r="D78">
-        <v>2428.727342804987</v>
+        <v>2424.579585580288</v>
       </c>
       <c r="E78">
-        <v>778.2640000000001</v>
+        <v>816.9029999999998</v>
       </c>
       <c r="F78">
-        <v>2936.564</v>
+        <v>2975.203</v>
       </c>
       <c r="G78">
         <v>189.4</v>
@@ -7811,28 +7811,28 @@
         <v>404.7</v>
       </c>
       <c r="M78">
-        <v>264.29076</v>
+        <v>267.76827</v>
       </c>
       <c r="N78">
-        <v>140.40924</v>
+        <v>136.93173</v>
       </c>
       <c r="O78">
-        <v>39.31458719999999</v>
+        <v>38.34088440000001</v>
       </c>
       <c r="P78">
-        <v>101.0946528</v>
+        <v>98.59084560000001</v>
       </c>
       <c r="Q78">
-        <v>206.3946528</v>
+        <v>203.8908456</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1765494666025618</v>
+        <v>0.181748941679546</v>
       </c>
       <c r="T78">
-        <v>3.01961816634092</v>
+        <v>3.139698422160415</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.53126806249299</v>
+        <v>1.511381464278796</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09169825658629557</v>
+        <v>0.1271522706568165</v>
       </c>
       <c r="C79">
-        <v>-361.2234144197123</v>
+        <v>-1456.514896867154</v>
       </c>
       <c r="D79">
-        <v>2424.579585580288</v>
+        <v>1367.927103132846</v>
       </c>
       <c r="E79">
-        <v>816.9029999999998</v>
+        <v>855.5419999999999</v>
       </c>
       <c r="F79">
-        <v>2975.203</v>
+        <v>3013.842</v>
       </c>
       <c r="G79">
         <v>189.4</v>
@@ -7893,45 +7893,45 @@
         <v>404.7</v>
       </c>
       <c r="M79">
-        <v>267.76827</v>
+        <v>442.4320056000001</v>
       </c>
       <c r="N79">
-        <v>136.93173</v>
+        <v>-37.73200560000009</v>
       </c>
       <c r="O79">
-        <v>38.34088440000001</v>
+        <v>-10.56496156800003</v>
       </c>
       <c r="P79">
-        <v>98.59084560000001</v>
+        <v>-27.16704403200006</v>
       </c>
       <c r="Q79">
-        <v>203.8908456</v>
+        <v>78.13295596799995</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.181748941679546</v>
+        <v>0.1907959844985558</v>
       </c>
       <c r="T79">
-        <v>3.139698422160415</v>
+        <v>3.348637055393897</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.28</v>
+        <v>0.2561207113538894</v>
       </c>
       <c r="W79">
-        <v>0.0648</v>
+        <v>0.109201479573249</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.511381464278796</v>
+        <v>0.9147168262638907</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1271522706568165</v>
+        <v>0.1281622706568165</v>
       </c>
       <c r="C80">
-        <v>-1456.514896867154</v>
+        <v>-1511.928645342958</v>
       </c>
       <c r="D80">
-        <v>1367.927103132846</v>
+        <v>1351.152354657042</v>
       </c>
       <c r="E80">
-        <v>855.5419999999999</v>
+        <v>894.181</v>
       </c>
       <c r="F80">
-        <v>3013.842</v>
+        <v>3052.481</v>
       </c>
       <c r="G80">
         <v>189.4</v>
@@ -7975,37 +7975,37 @@
         <v>404.7</v>
       </c>
       <c r="M80">
-        <v>442.4320056000001</v>
+        <v>448.1042108000001</v>
       </c>
       <c r="N80">
-        <v>-37.73200560000009</v>
+        <v>-43.4042108000001</v>
       </c>
       <c r="O80">
-        <v>-10.56496156800003</v>
+        <v>-12.15317902400003</v>
       </c>
       <c r="P80">
-        <v>-27.16704403200006</v>
+        <v>-31.25103177600007</v>
       </c>
       <c r="Q80">
-        <v>78.13295596799995</v>
+        <v>74.04896822399994</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1907959844985558</v>
+        <v>0.1977005551889632</v>
       </c>
       <c r="T80">
-        <v>3.348637055393897</v>
+        <v>3.508095962793607</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2561207113538894</v>
+        <v>0.2528786770329541</v>
       </c>
       <c r="W80">
-        <v>0.109201479573249</v>
+        <v>0.1096774102115624</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9147168262638907</v>
+        <v>0.9031381322605503</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1281622706568165</v>
+        <v>0.1291722706568165</v>
       </c>
       <c r="C81">
-        <v>-1511.928645342958</v>
+        <v>-1566.935963819265</v>
       </c>
       <c r="D81">
-        <v>1351.152354657042</v>
+        <v>1334.784036180735</v>
       </c>
       <c r="E81">
-        <v>894.181</v>
+        <v>932.8200000000002</v>
       </c>
       <c r="F81">
-        <v>3052.481</v>
+        <v>3091.12</v>
       </c>
       <c r="G81">
         <v>189.4</v>
@@ -8057,37 +8057,37 @@
         <v>404.7</v>
       </c>
       <c r="M81">
-        <v>448.1042108000001</v>
+        <v>453.7764160000001</v>
       </c>
       <c r="N81">
-        <v>-43.4042108000001</v>
+        <v>-49.07641600000011</v>
       </c>
       <c r="O81">
-        <v>-12.15317902400003</v>
+        <v>-13.74139648000003</v>
       </c>
       <c r="P81">
-        <v>-31.25103177600007</v>
+        <v>-35.33501952000007</v>
       </c>
       <c r="Q81">
-        <v>74.04896822399994</v>
+        <v>69.96498047999994</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1977005551889632</v>
+        <v>0.2052955829484114</v>
       </c>
       <c r="T81">
-        <v>3.508095962793607</v>
+        <v>3.683500760933288</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2528786770329541</v>
+        <v>0.2497176935700422</v>
       </c>
       <c r="W81">
-        <v>0.1096774102115624</v>
+        <v>0.1101414425839178</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9031381322605503</v>
+        <v>0.8918489056072934</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1291722706568165</v>
+        <v>0.1301822706568165</v>
       </c>
       <c r="C82">
-        <v>-1566.935963819265</v>
+        <v>-1621.551446391362</v>
       </c>
       <c r="D82">
-        <v>1334.784036180735</v>
+        <v>1318.807553608639</v>
       </c>
       <c r="E82">
-        <v>932.8200000000002</v>
+        <v>971.4590000000003</v>
       </c>
       <c r="F82">
-        <v>3091.12</v>
+        <v>3129.759</v>
       </c>
       <c r="G82">
         <v>189.4</v>
@@ -8139,37 +8139,37 @@
         <v>404.7</v>
       </c>
       <c r="M82">
-        <v>453.7764160000001</v>
+        <v>459.4486212000001</v>
       </c>
       <c r="N82">
-        <v>-49.07641600000011</v>
+        <v>-54.74862120000012</v>
       </c>
       <c r="O82">
-        <v>-13.74139648000003</v>
+        <v>-15.32961393600003</v>
       </c>
       <c r="P82">
-        <v>-35.33501952000007</v>
+        <v>-39.41900726400009</v>
       </c>
       <c r="Q82">
-        <v>69.96498047999994</v>
+        <v>65.88099273599993</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2052955829484114</v>
+        <v>0.2136900873141172</v>
       </c>
       <c r="T82">
-        <v>3.683500760933288</v>
+        <v>3.87736922203504</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2497176935700422</v>
+        <v>0.2466347590815231</v>
       </c>
       <c r="W82">
-        <v>0.1101414425839178</v>
+        <v>0.1105940173668324</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8918489056072934</v>
+        <v>0.880838425291154</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1301822706568165</v>
+        <v>0.1311922706568165</v>
       </c>
       <c r="C83">
-        <v>-1621.551446391362</v>
+        <v>-1675.788996692218</v>
       </c>
       <c r="D83">
-        <v>1318.807553608639</v>
+        <v>1303.209003307782</v>
       </c>
       <c r="E83">
-        <v>971.4590000000003</v>
+        <v>1010.098</v>
       </c>
       <c r="F83">
-        <v>3129.759</v>
+        <v>3168.398</v>
       </c>
       <c r="G83">
         <v>189.4</v>
@@ -8221,37 +8221,37 @@
         <v>404.7</v>
       </c>
       <c r="M83">
-        <v>459.4486212000001</v>
+        <v>465.1208264000001</v>
       </c>
       <c r="N83">
-        <v>-54.74862120000012</v>
+        <v>-60.42082640000007</v>
       </c>
       <c r="O83">
-        <v>-15.32961393600003</v>
+        <v>-16.91783139200002</v>
       </c>
       <c r="P83">
-        <v>-39.41900726400009</v>
+        <v>-43.50299500800004</v>
       </c>
       <c r="Q83">
-        <v>65.88099273599993</v>
+        <v>61.79700499199997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2136900873141172</v>
+        <v>0.2230173143871237</v>
       </c>
       <c r="T83">
-        <v>3.87736922203504</v>
+        <v>4.092778623259209</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2466347590815231</v>
+        <v>0.2436270181171143</v>
       </c>
       <c r="W83">
-        <v>0.1105940173668324</v>
+        <v>0.1110355537404076</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.880838425291154</v>
+        <v>0.8700964932754083</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1311922706568165</v>
+        <v>0.1322022706568165</v>
       </c>
       <c r="C84">
-        <v>-1675.788996692218</v>
+        <v>-1729.661868248312</v>
       </c>
       <c r="D84">
-        <v>1303.209003307782</v>
+        <v>1287.975131751688</v>
       </c>
       <c r="E84">
-        <v>1010.098</v>
+        <v>1048.737</v>
       </c>
       <c r="F84">
-        <v>3168.398</v>
+        <v>3207.037</v>
       </c>
       <c r="G84">
         <v>189.4</v>
@@ -8303,37 +8303,37 @@
         <v>404.7</v>
       </c>
       <c r="M84">
-        <v>465.1208264000001</v>
+        <v>470.7930316000001</v>
       </c>
       <c r="N84">
-        <v>-60.42082640000007</v>
+        <v>-66.09303160000007</v>
       </c>
       <c r="O84">
-        <v>-16.91783139200002</v>
+        <v>-18.50604884800002</v>
       </c>
       <c r="P84">
-        <v>-43.50299500800004</v>
+        <v>-47.58698275200005</v>
       </c>
       <c r="Q84">
-        <v>61.79700499199997</v>
+        <v>57.71301724799996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2230173143871237</v>
+        <v>0.2334418622922487</v>
       </c>
       <c r="T84">
-        <v>4.092778623259209</v>
+        <v>4.333530306980339</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2436270181171143</v>
+        <v>0.2406917528385949</v>
       </c>
       <c r="W84">
-        <v>0.1110355537404076</v>
+        <v>0.1114664506832943</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8700964932754083</v>
+        <v>0.8596134029949817</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1322022706568165</v>
+        <v>0.1332122706568165</v>
       </c>
       <c r="C85">
-        <v>-1729.661868248312</v>
+        <v>-1783.182702037717</v>
       </c>
       <c r="D85">
-        <v>1287.975131751688</v>
+        <v>1273.093297962283</v>
       </c>
       <c r="E85">
-        <v>1048.737</v>
+        <v>1087.376</v>
       </c>
       <c r="F85">
-        <v>3207.037</v>
+        <v>3245.676</v>
       </c>
       <c r="G85">
         <v>189.4</v>
@@ -8385,37 +8385,37 @@
         <v>404.7</v>
       </c>
       <c r="M85">
-        <v>470.7930316000001</v>
+        <v>476.4652368000001</v>
       </c>
       <c r="N85">
-        <v>-66.09303160000007</v>
+        <v>-71.76523680000014</v>
       </c>
       <c r="O85">
-        <v>-18.50604884800002</v>
+        <v>-20.09426630400004</v>
       </c>
       <c r="P85">
-        <v>-47.58698275200005</v>
+        <v>-51.67097049600009</v>
       </c>
       <c r="Q85">
-        <v>57.71301724799996</v>
+        <v>53.62902950399992</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2334418622922487</v>
+        <v>0.2451694786855142</v>
       </c>
       <c r="T85">
-        <v>4.333530306980339</v>
+        <v>4.60437595116661</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2406917528385949</v>
+        <v>0.2378263748286116</v>
       </c>
       <c r="W85">
-        <v>0.1114664506832943</v>
+        <v>0.1118870881751598</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8596134029949817</v>
+        <v>0.8493799101021842</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1332122706568165</v>
+        <v>0.1342222706568165</v>
       </c>
       <c r="C86">
-        <v>-1783.182702037717</v>
+        <v>-1836.363561474153</v>
       </c>
       <c r="D86">
-        <v>1273.093297962283</v>
+        <v>1258.551438525847</v>
       </c>
       <c r="E86">
-        <v>1087.376</v>
+        <v>1126.015</v>
       </c>
       <c r="F86">
-        <v>3245.676</v>
+        <v>3284.315</v>
       </c>
       <c r="G86">
         <v>189.4</v>
@@ -8467,37 +8467,37 @@
         <v>404.7</v>
       </c>
       <c r="M86">
-        <v>476.4652368</v>
+        <v>482.1374420000001</v>
       </c>
       <c r="N86">
-        <v>-71.76523680000003</v>
+        <v>-77.43744200000009</v>
       </c>
       <c r="O86">
-        <v>-20.09426630400001</v>
+        <v>-21.68248376000003</v>
       </c>
       <c r="P86">
-        <v>-51.67097049600002</v>
+        <v>-55.75495824000006</v>
       </c>
       <c r="Q86">
-        <v>53.62902950399999</v>
+        <v>49.54504175999995</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2451694786855141</v>
+        <v>0.2584607772645484</v>
       </c>
       <c r="T86">
-        <v>4.604375951166608</v>
+        <v>4.911334347911049</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2378263748286117</v>
+        <v>0.2350284174776868</v>
       </c>
       <c r="W86">
-        <v>0.1118870881751598</v>
+        <v>0.1122978283142756</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8493799101021844</v>
+        <v>0.8393872052774527</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1342222706568165</v>
+        <v>0.1352322706568165</v>
       </c>
       <c r="C87">
-        <v>-1836.363561474153</v>
+        <v>-1889.215965020496</v>
       </c>
       <c r="D87">
-        <v>1258.551438525847</v>
+        <v>1244.338034979505</v>
       </c>
       <c r="E87">
-        <v>1126.015</v>
+        <v>1164.654</v>
       </c>
       <c r="F87">
-        <v>3284.315</v>
+        <v>3322.954</v>
       </c>
       <c r="G87">
         <v>189.4</v>
@@ -8549,37 +8549,37 @@
         <v>404.7</v>
       </c>
       <c r="M87">
-        <v>482.1374420000001</v>
+        <v>487.8096472000001</v>
       </c>
       <c r="N87">
-        <v>-77.43744200000009</v>
+        <v>-83.1096472000001</v>
       </c>
       <c r="O87">
-        <v>-21.68248376000003</v>
+        <v>-23.27070121600003</v>
       </c>
       <c r="P87">
-        <v>-55.75495824000006</v>
+        <v>-59.83894598400006</v>
       </c>
       <c r="Q87">
-        <v>49.54504175999995</v>
+        <v>45.46105401599995</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2584607772645484</v>
+        <v>0.2736508327834447</v>
       </c>
       <c r="T87">
-        <v>4.911334347911049</v>
+        <v>5.262143944190409</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2350284174776868</v>
+        <v>0.2322955289023648</v>
       </c>
       <c r="W87">
-        <v>0.1122978283142756</v>
+        <v>0.1126990163571329</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8393872052774527</v>
+        <v>0.8296268889370171</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1352322706568165</v>
+        <v>0.1362422706568165</v>
       </c>
       <c r="C88">
-        <v>-1889.215965020496</v>
+        <v>-1941.750916617047</v>
       </c>
       <c r="D88">
-        <v>1244.338034979505</v>
+        <v>1230.442083382953</v>
       </c>
       <c r="E88">
-        <v>1164.654</v>
+        <v>1203.293</v>
       </c>
       <c r="F88">
-        <v>3322.954</v>
+        <v>3361.593</v>
       </c>
       <c r="G88">
         <v>189.4</v>
@@ -8631,37 +8631,37 @@
         <v>404.7</v>
       </c>
       <c r="M88">
-        <v>487.8096472000001</v>
+        <v>493.4818524</v>
       </c>
       <c r="N88">
-        <v>-83.1096472000001</v>
+        <v>-88.78185240000005</v>
       </c>
       <c r="O88">
-        <v>-23.27070121600003</v>
+        <v>-24.85891867200002</v>
       </c>
       <c r="P88">
-        <v>-59.83894598400006</v>
+        <v>-63.92293372800003</v>
       </c>
       <c r="Q88">
-        <v>45.46105401599995</v>
+        <v>41.37706627199998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2736508327834447</v>
+        <v>0.2911778199206327</v>
       </c>
       <c r="T88">
-        <v>5.262143944190409</v>
+        <v>5.666924247589671</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2322955289023648</v>
+        <v>0.229625465351763</v>
       </c>
       <c r="W88">
-        <v>0.1126990163571329</v>
+        <v>0.1130909816863612</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8296268889370171</v>
+        <v>0.8200909476848677</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1362422706568165</v>
+        <v>0.1372522706568165</v>
       </c>
       <c r="C89">
-        <v>-1941.750916617047</v>
+        <v>-1993.9789340935</v>
       </c>
       <c r="D89">
-        <v>1230.442083382953</v>
+        <v>1216.8530659065</v>
       </c>
       <c r="E89">
-        <v>1203.293</v>
+        <v>1241.932</v>
       </c>
       <c r="F89">
-        <v>3361.593</v>
+        <v>3400.232</v>
       </c>
       <c r="G89">
         <v>189.4</v>
@@ -8713,37 +8713,37 @@
         <v>404.7</v>
       </c>
       <c r="M89">
-        <v>493.4818524</v>
+        <v>499.1540576</v>
       </c>
       <c r="N89">
-        <v>-88.78185240000005</v>
+        <v>-94.45405760000006</v>
       </c>
       <c r="O89">
-        <v>-24.85891867200002</v>
+        <v>-26.44713612800002</v>
       </c>
       <c r="P89">
-        <v>-63.92293372800003</v>
+        <v>-68.00692147200004</v>
       </c>
       <c r="Q89">
-        <v>41.37706627199998</v>
+        <v>37.29307852799997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2911778199206327</v>
+        <v>0.3116259715806856</v>
       </c>
       <c r="T89">
-        <v>5.666924247589671</v>
+        <v>6.139167934888812</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.229625465351763</v>
+        <v>0.2270160850636747</v>
       </c>
       <c r="W89">
-        <v>0.1130909816863612</v>
+        <v>0.1134740387126526</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8200909476848677</v>
+        <v>0.8107717323702668</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1372522706568165</v>
+        <v>0.1382622706568165</v>
       </c>
       <c r="C90">
-        <v>-1993.9789340935</v>
+        <v>-2045.910075718782</v>
       </c>
       <c r="D90">
-        <v>1216.8530659065</v>
+        <v>1203.560924281218</v>
       </c>
       <c r="E90">
-        <v>1241.932</v>
+        <v>1280.571</v>
       </c>
       <c r="F90">
-        <v>3400.232</v>
+        <v>3438.871</v>
       </c>
       <c r="G90">
         <v>189.4</v>
@@ -8795,37 +8795,37 @@
         <v>404.7</v>
       </c>
       <c r="M90">
-        <v>499.1540576</v>
+        <v>504.8262628000001</v>
       </c>
       <c r="N90">
-        <v>-94.45405760000006</v>
+        <v>-100.1262628000001</v>
       </c>
       <c r="O90">
-        <v>-26.44713612800002</v>
+        <v>-28.03535358400002</v>
       </c>
       <c r="P90">
-        <v>-68.00692147200004</v>
+        <v>-72.09090921600004</v>
       </c>
       <c r="Q90">
-        <v>37.29307852799997</v>
+        <v>33.20909078399997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3116259715806856</v>
+        <v>0.3357919689971115</v>
       </c>
       <c r="T90">
-        <v>6.139167934888812</v>
+        <v>6.697274110787794</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2270160850636747</v>
+        <v>0.2244653425348694</v>
       </c>
       <c r="W90">
-        <v>0.1134740387126526</v>
+        <v>0.1138484877158812</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8107717323702668</v>
+        <v>0.8016619376245335</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1382622706568165</v>
+        <v>0.1900138562446083</v>
       </c>
       <c r="C91">
-        <v>-2045.910075718782</v>
+        <v>-2516.450612818065</v>
       </c>
       <c r="D91">
-        <v>1203.560924281218</v>
+        <v>771.6593871819355</v>
       </c>
       <c r="E91">
-        <v>1280.571</v>
+        <v>1319.21</v>
       </c>
       <c r="F91">
-        <v>3438.871</v>
+        <v>3477.51</v>
       </c>
       <c r="G91">
         <v>189.4</v>
@@ -8877,45 +8877,45 @@
         <v>404.7</v>
       </c>
       <c r="M91">
-        <v>504.8262628000001</v>
+        <v>698.2840080000001</v>
       </c>
       <c r="N91">
-        <v>-100.1262628000001</v>
+        <v>-293.5840080000001</v>
       </c>
       <c r="O91">
-        <v>-28.03535358400002</v>
+        <v>-82.20352224000004</v>
       </c>
       <c r="P91">
-        <v>-72.09090921600004</v>
+        <v>-211.3804857600001</v>
       </c>
       <c r="Q91">
-        <v>33.20909078399997</v>
+        <v>-106.08048576</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3357919689971115</v>
+        <v>0.3862070217747411</v>
       </c>
       <c r="T91">
-        <v>6.697274110787794</v>
+        <v>7.861594036368156</v>
       </c>
       <c r="U91">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.2244653425348694</v>
+        <v>0.1622778106068269</v>
       </c>
       <c r="W91">
-        <v>0.1138484877158812</v>
+        <v>0.1682146156301492</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8016619376245335</v>
+        <v>0.579563609310096</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1900138562446083</v>
+        <v>0.1915638562446084</v>
       </c>
       <c r="C92">
-        <v>-2516.450612818065</v>
+        <v>-2563.295158972969</v>
       </c>
       <c r="D92">
-        <v>771.6593871819355</v>
+        <v>763.4538410270311</v>
       </c>
       <c r="E92">
-        <v>1319.21</v>
+        <v>1357.849</v>
       </c>
       <c r="F92">
-        <v>3477.51</v>
+        <v>3516.149</v>
       </c>
       <c r="G92">
         <v>189.4</v>
@@ -8959,37 +8959,37 @@
         <v>404.7</v>
       </c>
       <c r="M92">
-        <v>698.2840080000001</v>
+        <v>706.0427192000001</v>
       </c>
       <c r="N92">
-        <v>-293.5840080000001</v>
+        <v>-301.3427192000001</v>
       </c>
       <c r="O92">
-        <v>-82.20352224000004</v>
+        <v>-84.37596137600003</v>
       </c>
       <c r="P92">
-        <v>-211.3804857600001</v>
+        <v>-216.9667578240001</v>
       </c>
       <c r="Q92">
-        <v>-106.08048576</v>
+        <v>-111.6667578240001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3862070217747411</v>
+        <v>0.4240300241941568</v>
       </c>
       <c r="T92">
-        <v>7.861594036368156</v>
+        <v>8.735104484853506</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1622778106068269</v>
+        <v>0.1604945379627958</v>
       </c>
       <c r="W92">
-        <v>0.1682146156301492</v>
+        <v>0.1685726967770706</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.579563609310096</v>
+        <v>0.5731947784385565</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1915638562446084</v>
+        <v>0.1931138562446084</v>
       </c>
       <c r="C93">
-        <v>-2563.295158972969</v>
+        <v>-2609.967031669119</v>
       </c>
       <c r="D93">
-        <v>763.4538410270311</v>
+        <v>755.420968330881</v>
       </c>
       <c r="E93">
-        <v>1357.849</v>
+        <v>1396.488</v>
       </c>
       <c r="F93">
-        <v>3516.149</v>
+        <v>3554.788</v>
       </c>
       <c r="G93">
         <v>189.4</v>
@@ -9041,37 +9041,37 @@
         <v>404.7</v>
       </c>
       <c r="M93">
-        <v>706.0427192000001</v>
+        <v>713.8014304000001</v>
       </c>
       <c r="N93">
-        <v>-301.3427192000001</v>
+        <v>-309.1014304000001</v>
       </c>
       <c r="O93">
-        <v>-84.37596137600003</v>
+        <v>-86.54840051200003</v>
       </c>
       <c r="P93">
-        <v>-216.9667578240001</v>
+        <v>-222.5530298880001</v>
       </c>
       <c r="Q93">
-        <v>-111.6667578240001</v>
+        <v>-117.253029888</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4240300241941568</v>
+        <v>0.4713087772184266</v>
       </c>
       <c r="T93">
-        <v>8.735104484853506</v>
+        <v>9.826992545460199</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1604945379627958</v>
+        <v>0.1587500321153741</v>
       </c>
       <c r="W93">
-        <v>0.1685726967770706</v>
+        <v>0.1689229935512329</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5731947784385565</v>
+        <v>0.5669644004120504</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1931138562446084</v>
+        <v>0.1946638562446084</v>
       </c>
       <c r="C94">
-        <v>-2609.967031669119</v>
+        <v>-2656.471624637427</v>
       </c>
       <c r="D94">
-        <v>755.420968330881</v>
+        <v>747.5553753625727</v>
       </c>
       <c r="E94">
-        <v>1396.488</v>
+        <v>1435.127</v>
       </c>
       <c r="F94">
-        <v>3554.788</v>
+        <v>3593.427</v>
       </c>
       <c r="G94">
         <v>189.4</v>
@@ -9123,37 +9123,37 @@
         <v>404.7</v>
       </c>
       <c r="M94">
-        <v>713.8014304000001</v>
+        <v>721.5601416000001</v>
       </c>
       <c r="N94">
-        <v>-309.1014304000001</v>
+        <v>-316.8601416000001</v>
       </c>
       <c r="O94">
-        <v>-86.54840051200003</v>
+        <v>-88.72083964800002</v>
       </c>
       <c r="P94">
-        <v>-222.5530298880001</v>
+        <v>-228.139301952</v>
       </c>
       <c r="Q94">
-        <v>-117.253029888</v>
+        <v>-122.839301952</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4713087772184266</v>
+        <v>0.5320957453924875</v>
       </c>
       <c r="T94">
-        <v>9.826992545460199</v>
+        <v>11.23084862338308</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1587500321153741</v>
+        <v>0.1570430425227357</v>
       </c>
       <c r="W94">
-        <v>0.1689229935512329</v>
+        <v>0.1692657570614347</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5669644004120504</v>
+        <v>0.5608680090097704</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1946638562446084</v>
+        <v>0.1962138562446084</v>
       </c>
       <c r="C95">
-        <v>-2656.471624637427</v>
+        <v>-2702.81410928134</v>
       </c>
       <c r="D95">
-        <v>747.5553753625727</v>
+        <v>739.8518907186601</v>
       </c>
       <c r="E95">
-        <v>1435.127</v>
+        <v>1473.766</v>
       </c>
       <c r="F95">
-        <v>3593.427</v>
+        <v>3632.066</v>
       </c>
       <c r="G95">
         <v>189.4</v>
@@ -9205,37 +9205,37 @@
         <v>404.7</v>
       </c>
       <c r="M95">
-        <v>721.5601416000001</v>
+        <v>729.3188528000001</v>
       </c>
       <c r="N95">
-        <v>-316.8601416000001</v>
+        <v>-324.6188528000001</v>
       </c>
       <c r="O95">
-        <v>-88.72083964800002</v>
+        <v>-90.89327878400003</v>
       </c>
       <c r="P95">
-        <v>-228.139301952</v>
+        <v>-233.7255740160001</v>
       </c>
       <c r="Q95">
-        <v>-122.839301952</v>
+        <v>-128.425574016</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5320957453924875</v>
+        <v>0.6131450362912355</v>
       </c>
       <c r="T95">
-        <v>11.23084862338308</v>
+        <v>13.10265672728027</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1570430425227357</v>
+        <v>0.1553723718576002</v>
       </c>
       <c r="W95">
-        <v>0.1692657570614347</v>
+        <v>0.1696012277309939</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5608680090097704</v>
+        <v>0.5549013280628579</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1962138562446084</v>
+        <v>0.1977638562446084</v>
       </c>
       <c r="C96">
-        <v>-2702.81410928134</v>
+        <v>-2748.999446015307</v>
       </c>
       <c r="D96">
-        <v>739.8518907186601</v>
+        <v>732.3055539846935</v>
       </c>
       <c r="E96">
-        <v>1473.766</v>
+        <v>1512.405</v>
       </c>
       <c r="F96">
-        <v>3632.066</v>
+        <v>3670.705</v>
       </c>
       <c r="G96">
         <v>189.4</v>
@@ -9287,37 +9287,37 @@
         <v>404.7</v>
       </c>
       <c r="M96">
-        <v>729.3188528000001</v>
+        <v>737.0775640000001</v>
       </c>
       <c r="N96">
-        <v>-324.6188528000001</v>
+        <v>-332.3775640000001</v>
       </c>
       <c r="O96">
-        <v>-90.89327878400003</v>
+        <v>-93.06571792000003</v>
       </c>
       <c r="P96">
-        <v>-233.7255740160001</v>
+        <v>-239.31184608</v>
       </c>
       <c r="Q96">
-        <v>-128.425574016</v>
+        <v>-134.01184608</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6131450362912355</v>
+        <v>0.7266140435494831</v>
       </c>
       <c r="T96">
-        <v>13.10265672728027</v>
+        <v>15.72318807273633</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1553723718576002</v>
+        <v>0.1537368732064676</v>
       </c>
       <c r="W96">
-        <v>0.1696012277309939</v>
+        <v>0.1699296358601413</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5549013280628579</v>
+        <v>0.54906026145167</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1977638562446084</v>
+        <v>0.1993138562446084</v>
       </c>
       <c r="C97">
-        <v>-2748.999446015307</v>
+        <v>-2795.032394916361</v>
       </c>
       <c r="D97">
-        <v>732.3055539846935</v>
+        <v>724.9116050836399</v>
       </c>
       <c r="E97">
-        <v>1512.405</v>
+        <v>1551.044</v>
       </c>
       <c r="F97">
-        <v>3670.705</v>
+        <v>3709.344000000001</v>
       </c>
       <c r="G97">
         <v>189.4</v>
@@ -9369,37 +9369,37 @@
         <v>404.7</v>
       </c>
       <c r="M97">
-        <v>737.0775640000001</v>
+        <v>744.8362752000002</v>
       </c>
       <c r="N97">
-        <v>-332.3775640000001</v>
+        <v>-340.1362752000002</v>
       </c>
       <c r="O97">
-        <v>-93.06571792000003</v>
+        <v>-95.23815705600006</v>
       </c>
       <c r="P97">
-        <v>-239.31184608</v>
+        <v>-244.8981181440001</v>
       </c>
       <c r="Q97">
-        <v>-134.01184608</v>
+        <v>-139.5981181440001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7266140435494831</v>
+        <v>0.8968175544368542</v>
       </c>
       <c r="T97">
-        <v>15.72318807273633</v>
+        <v>19.65398509092042</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1537368732064676</v>
+        <v>0.1521354474439002</v>
       </c>
       <c r="W97">
-        <v>0.1699296358601413</v>
+        <v>0.1702512021532649</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.54906026145167</v>
+        <v>0.543340883728215</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1993138562446084</v>
+        <v>0.2008638562446084</v>
       </c>
       <c r="C98">
-        <v>-2795.03239491636</v>
+        <v>-2840.91752573686</v>
       </c>
       <c r="D98">
-        <v>724.9116050836399</v>
+        <v>717.6654742631399</v>
       </c>
       <c r="E98">
-        <v>1551.044</v>
+        <v>1589.683</v>
       </c>
       <c r="F98">
-        <v>3709.344</v>
+        <v>3747.983</v>
       </c>
       <c r="G98">
         <v>189.4</v>
@@ -9451,37 +9451,37 @@
         <v>404.7</v>
       </c>
       <c r="M98">
-        <v>744.8362752</v>
+        <v>752.5949864</v>
       </c>
       <c r="N98">
-        <v>-340.1362752000001</v>
+        <v>-347.8949864000001</v>
       </c>
       <c r="O98">
-        <v>-95.23815705600002</v>
+        <v>-97.41059619200003</v>
       </c>
       <c r="P98">
-        <v>-244.898118144</v>
+        <v>-250.484390208</v>
       </c>
       <c r="Q98">
-        <v>-139.598118144</v>
+        <v>-145.184390208</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8968175544368518</v>
+        <v>1.180490072582469</v>
       </c>
       <c r="T98">
-        <v>19.65398509092037</v>
+        <v>26.20531345456049</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1521354474439002</v>
+        <v>0.1505670407692208</v>
       </c>
       <c r="W98">
-        <v>0.1702512021532649</v>
+        <v>0.1705661382135405</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.543340883728215</v>
+        <v>0.5377394313186459</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2008638562446084</v>
+        <v>0.2024138562446083</v>
       </c>
       <c r="C99">
-        <v>-2840.91752573686</v>
+        <v>-2886.659227322667</v>
       </c>
       <c r="D99">
-        <v>717.6654742631399</v>
+        <v>710.5627726773334</v>
       </c>
       <c r="E99">
-        <v>1589.683</v>
+        <v>1628.322</v>
       </c>
       <c r="F99">
-        <v>3747.983</v>
+        <v>3786.622</v>
       </c>
       <c r="G99">
         <v>189.4</v>
@@ -9533,37 +9533,37 @@
         <v>404.7</v>
       </c>
       <c r="M99">
-        <v>752.5949864</v>
+        <v>760.3536976</v>
       </c>
       <c r="N99">
-        <v>-347.8949864000001</v>
+        <v>-355.6536976</v>
       </c>
       <c r="O99">
-        <v>-97.41059619200003</v>
+        <v>-99.58303532800002</v>
       </c>
       <c r="P99">
-        <v>-250.484390208</v>
+        <v>-256.070662272</v>
       </c>
       <c r="Q99">
-        <v>-145.184390208</v>
+        <v>-150.770662272</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.180490072582469</v>
+        <v>1.747835108873704</v>
       </c>
       <c r="T99">
-        <v>26.20531345456049</v>
+        <v>39.30797018184074</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1505670407692208</v>
+        <v>0.1490306423940247</v>
       </c>
       <c r="W99">
-        <v>0.1705661382135405</v>
+        <v>0.1708746470072798</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5377394313186459</v>
+        <v>0.5322522942643739</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2024138562446083</v>
+        <v>0.2039638562446083</v>
       </c>
       <c r="C100">
-        <v>-2886.659227322667</v>
+        <v>-2932.261716477525</v>
       </c>
       <c r="D100">
-        <v>710.5627726773334</v>
+        <v>703.5992835224749</v>
       </c>
       <c r="E100">
-        <v>1628.322</v>
+        <v>1666.961</v>
       </c>
       <c r="F100">
-        <v>3786.622</v>
+        <v>3825.261</v>
       </c>
       <c r="G100">
         <v>189.4</v>
@@ -9615,37 +9615,37 @@
         <v>404.7</v>
       </c>
       <c r="M100">
-        <v>760.3536976</v>
+        <v>768.1124088</v>
       </c>
       <c r="N100">
-        <v>-355.6536976</v>
+        <v>-363.4124088</v>
       </c>
       <c r="O100">
-        <v>-99.58303532800002</v>
+        <v>-101.755474464</v>
       </c>
       <c r="P100">
-        <v>-256.070662272</v>
+        <v>-261.656934336</v>
       </c>
       <c r="Q100">
-        <v>-150.770662272</v>
+        <v>-156.356934336</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.747835108873704</v>
+        <v>3.449870217747407</v>
       </c>
       <c r="T100">
-        <v>39.30797018184074</v>
+        <v>78.61594036368147</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1490306423940247</v>
+        <v>0.1475252823698426</v>
       </c>
       <c r="W100">
-        <v>0.1708746470072798</v>
+        <v>0.1711769233001356</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5322522942643739</v>
+        <v>0.5268760084637236</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2039638562446083</v>
-      </c>
-      <c r="C101">
-        <v>-2932.261716477525</v>
-      </c>
-      <c r="D101">
-        <v>703.5992835224749</v>
-      </c>
-      <c r="E101">
-        <v>1666.961</v>
-      </c>
-      <c r="F101">
-        <v>3825.261</v>
-      </c>
-      <c r="G101">
-        <v>189.4</v>
-      </c>
-      <c r="H101">
-        <v>1705.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>510</v>
-      </c>
-      <c r="K101">
-        <v>105.3</v>
-      </c>
-      <c r="L101">
-        <v>404.7</v>
-      </c>
-      <c r="M101">
-        <v>768.1124088</v>
-      </c>
-      <c r="N101">
-        <v>-363.4124088</v>
-      </c>
-      <c r="O101">
-        <v>-101.755474464</v>
-      </c>
-      <c r="P101">
-        <v>-261.656934336</v>
-      </c>
-      <c r="Q101">
-        <v>-156.356934336</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.449870217747407</v>
-      </c>
-      <c r="T101">
-        <v>78.61594036368147</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1475252823698426</v>
-      </c>
-      <c r="W101">
-        <v>0.1711769233001356</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5268760084637236</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
